--- a/research/traditional_assets/database/data/mexico/mexico_trucking.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_trucking.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1026891454829138</v>
+        <v>0.1024125780464651</v>
       </c>
       <c r="C2">
-        <v>1067.314187238032</v>
+        <v>1060.274773793516</v>
       </c>
       <c r="D2">
-        <v>997.8141872380316</v>
+        <v>1002.688773793516</v>
       </c>
       <c r="E2">
-        <v>-684.2</v>
+        <v>-672.2860000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.914</v>
       </c>
       <c r="G2">
         <v>69.5</v>
@@ -1457,28 +1457,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5992742000000001</v>
       </c>
       <c r="N2">
-        <v>204.4666666666667</v>
+        <v>203.8673924666667</v>
       </c>
       <c r="O2">
-        <v>61.34</v>
+        <v>61.16021774000001</v>
       </c>
       <c r="P2">
-        <v>143.1266666666667</v>
+        <v>142.7071747266667</v>
       </c>
       <c r="Q2">
-        <v>227.3266666666667</v>
+        <v>226.9071747266667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1026891454829138</v>
+        <v>0.1030913919661264</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.833659560545123</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>341.1905045581249</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1024125780464651</v>
+        <v>0.1021360106100164</v>
       </c>
       <c r="C3">
-        <v>1060.274773793516</v>
+        <v>1053.283221455699</v>
       </c>
       <c r="D3">
-        <v>1002.688773793516</v>
+        <v>1007.611221455699</v>
       </c>
       <c r="E3">
-        <v>-672.2860000000001</v>
+        <v>-660.3720000000001</v>
       </c>
       <c r="F3">
-        <v>11.914</v>
+        <v>23.828</v>
       </c>
       <c r="G3">
         <v>69.5</v>
@@ -1539,28 +1539,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M3">
-        <v>0.5992742000000001</v>
+        <v>1.1985484</v>
       </c>
       <c r="N3">
-        <v>203.8673924666667</v>
+        <v>203.2681182666667</v>
       </c>
       <c r="O3">
-        <v>61.16021774000001</v>
+        <v>60.98043548000001</v>
       </c>
       <c r="P3">
-        <v>142.7071747266667</v>
+        <v>142.2876827866667</v>
       </c>
       <c r="Q3">
-        <v>226.9071747266667</v>
+        <v>226.4876827866667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1030913919661264</v>
+        <v>0.1035018475612412</v>
       </c>
       <c r="T3">
-        <v>0.833659560545123</v>
+        <v>0.8396321895789756</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>341.1905045581249</v>
+        <v>170.5952522790625</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1021360106100164</v>
+        <v>0.1018594431735676</v>
       </c>
       <c r="C4">
-        <v>1053.283221455699</v>
+        <v>1046.340238588213</v>
       </c>
       <c r="D4">
-        <v>1007.611221455699</v>
+        <v>1012.582238588213</v>
       </c>
       <c r="E4">
-        <v>-660.3720000000001</v>
+        <v>-648.4580000000001</v>
       </c>
       <c r="F4">
-        <v>23.828</v>
+        <v>35.742</v>
       </c>
       <c r="G4">
         <v>69.5</v>
@@ -1621,28 +1621,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M4">
-        <v>1.1985484</v>
+        <v>1.7978226</v>
       </c>
       <c r="N4">
-        <v>203.2681182666667</v>
+        <v>202.6688440666667</v>
       </c>
       <c r="O4">
-        <v>60.98043548000001</v>
+        <v>60.80065322000001</v>
       </c>
       <c r="P4">
-        <v>142.2876827866667</v>
+        <v>141.8681908466667</v>
       </c>
       <c r="Q4">
-        <v>226.4876827866667</v>
+        <v>226.0681908466667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1035018475612412</v>
+        <v>0.1039207661583171</v>
       </c>
       <c r="T4">
-        <v>0.8396321895789756</v>
+        <v>0.8457279656032166</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>170.5952522790625</v>
+        <v>113.7301681860417</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1018594431735676</v>
+        <v>0.1015828757371189</v>
       </c>
       <c r="C5">
-        <v>1046.340238588213</v>
+        <v>1039.44654760275</v>
       </c>
       <c r="D5">
-        <v>1012.582238588213</v>
+        <v>1017.60254760275</v>
       </c>
       <c r="E5">
-        <v>-648.4580000000001</v>
+        <v>-636.5440000000001</v>
       </c>
       <c r="F5">
-        <v>35.742</v>
+        <v>47.65600000000001</v>
       </c>
       <c r="G5">
         <v>69.5</v>
@@ -1703,28 +1703,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M5">
-        <v>1.7978226</v>
+        <v>2.3970968</v>
       </c>
       <c r="N5">
-        <v>202.6688440666667</v>
+        <v>202.0695698666667</v>
       </c>
       <c r="O5">
-        <v>60.80065322000001</v>
+        <v>60.62087096</v>
       </c>
       <c r="P5">
-        <v>141.8681908466667</v>
+        <v>141.4486989066667</v>
       </c>
       <c r="Q5">
-        <v>226.0681908466667</v>
+        <v>225.6486989066667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1039207661583171</v>
+        <v>0.1043484122261655</v>
       </c>
       <c r="T5">
-        <v>0.8457279656032166</v>
+        <v>0.8519507369612961</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>113.7301681860417</v>
+        <v>85.29762613953122</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1015828757371189</v>
+        <v>0.1013063083006701</v>
       </c>
       <c r="C6">
-        <v>1039.44654760275</v>
+        <v>1032.602885309047</v>
       </c>
       <c r="D6">
-        <v>1017.60254760275</v>
+        <v>1022.672885309047</v>
       </c>
       <c r="E6">
-        <v>-636.5440000000001</v>
+        <v>-624.63</v>
       </c>
       <c r="F6">
-        <v>47.65600000000001</v>
+        <v>59.57000000000001</v>
       </c>
       <c r="G6">
         <v>69.5</v>
@@ -1785,28 +1785,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M6">
-        <v>2.3970968</v>
+        <v>2.996371</v>
       </c>
       <c r="N6">
-        <v>202.0695698666667</v>
+        <v>201.4702956666667</v>
       </c>
       <c r="O6">
-        <v>60.62087096</v>
+        <v>60.4410887</v>
       </c>
       <c r="P6">
-        <v>141.4486989066667</v>
+        <v>141.0292069666667</v>
       </c>
       <c r="Q6">
-        <v>225.6486989066667</v>
+        <v>225.2292069666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1043484122261655</v>
+        <v>0.1047850613691265</v>
       </c>
       <c r="T6">
-        <v>0.8519507369612961</v>
+        <v>0.8583045140321773</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.29762613953122</v>
+        <v>68.23810091162498</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1013063083006701</v>
+        <v>0.1010297408642214</v>
       </c>
       <c r="C7">
-        <v>1032.602885309047</v>
+        <v>1025.810003275378</v>
       </c>
       <c r="D7">
-        <v>1022.672885309047</v>
+        <v>1027.794003275377</v>
       </c>
       <c r="E7">
-        <v>-624.63</v>
+        <v>-612.716</v>
       </c>
       <c r="F7">
-        <v>59.57000000000001</v>
+        <v>71.48400000000001</v>
       </c>
       <c r="G7">
         <v>69.5</v>
@@ -1867,28 +1867,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M7">
-        <v>2.996371</v>
+        <v>3.5956452</v>
       </c>
       <c r="N7">
-        <v>201.4702956666667</v>
+        <v>200.8710214666667</v>
       </c>
       <c r="O7">
-        <v>60.4410887</v>
+        <v>60.26130644000001</v>
       </c>
       <c r="P7">
-        <v>141.0292069666667</v>
+        <v>140.6097150266667</v>
       </c>
       <c r="Q7">
-        <v>225.2292069666667</v>
+        <v>224.8097150266667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1047850613691265</v>
+        <v>0.1052310009193844</v>
       </c>
       <c r="T7">
-        <v>0.8583045140321773</v>
+        <v>0.8647934778492474</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.23810091162498</v>
+        <v>56.86508409302082</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1010297408642214</v>
+        <v>0.1007531734277727</v>
       </c>
       <c r="C8">
-        <v>1025.810003275378</v>
+        <v>1019.06866819994</v>
       </c>
       <c r="D8">
-        <v>1027.794003275377</v>
+        <v>1032.96666819994</v>
       </c>
       <c r="E8">
-        <v>-612.716</v>
+        <v>-600.802</v>
       </c>
       <c r="F8">
-        <v>71.48400000000001</v>
+        <v>83.398</v>
       </c>
       <c r="G8">
         <v>69.5</v>
@@ -1949,28 +1949,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M8">
-        <v>3.5956452</v>
+        <v>4.1949194</v>
       </c>
       <c r="N8">
-        <v>200.8710214666667</v>
+        <v>200.2717472666667</v>
       </c>
       <c r="O8">
-        <v>60.26130644000001</v>
+        <v>60.08152418</v>
       </c>
       <c r="P8">
-        <v>140.6097150266667</v>
+        <v>140.1902230866667</v>
       </c>
       <c r="Q8">
-        <v>224.8097150266667</v>
+        <v>224.3902230866667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1052310009193844</v>
+        <v>0.1056865305674975</v>
       </c>
       <c r="T8">
-        <v>0.8647934778492474</v>
+        <v>0.8714219892752869</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.86508409302082</v>
+        <v>48.74150065116071</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1007531734277726</v>
+        <v>0.1004766059913239</v>
       </c>
       <c r="C9">
-        <v>1019.06866819994</v>
+        <v>1012.379662293509</v>
       </c>
       <c r="D9">
-        <v>1032.96666819994</v>
+        <v>1038.191662293509</v>
       </c>
       <c r="E9">
-        <v>-600.802</v>
+        <v>-588.888</v>
       </c>
       <c r="F9">
-        <v>83.39800000000001</v>
+        <v>95.31200000000001</v>
       </c>
       <c r="G9">
         <v>69.5</v>
@@ -2031,28 +2031,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M9">
-        <v>4.194919400000001</v>
+        <v>4.794193600000001</v>
       </c>
       <c r="N9">
-        <v>200.2717472666667</v>
+        <v>199.6724730666667</v>
       </c>
       <c r="O9">
-        <v>60.08152418</v>
+        <v>59.90174192000001</v>
       </c>
       <c r="P9">
-        <v>140.1902230866667</v>
+        <v>139.7707311466667</v>
       </c>
       <c r="Q9">
-        <v>224.3902230866667</v>
+        <v>223.9707311466667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1056865305674975</v>
+        <v>0.1061519630340477</v>
       </c>
       <c r="T9">
-        <v>0.8714219892752869</v>
+        <v>0.8781945987758055</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.7415006511607</v>
+        <v>42.64881306976562</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1004766059913239</v>
+        <v>0.1002000385548752</v>
       </c>
       <c r="C10">
-        <v>1012.379662293509</v>
+        <v>1005.74378367376</v>
       </c>
       <c r="D10">
-        <v>1038.191662293509</v>
+        <v>1043.46978367376</v>
       </c>
       <c r="E10">
-        <v>-588.888</v>
+        <v>-576.974</v>
       </c>
       <c r="F10">
-        <v>95.31200000000001</v>
+        <v>107.226</v>
       </c>
       <c r="G10">
         <v>69.5</v>
@@ -2113,28 +2113,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M10">
-        <v>4.794193600000001</v>
+        <v>5.3934678</v>
       </c>
       <c r="N10">
-        <v>199.6724730666667</v>
+        <v>199.0731988666667</v>
       </c>
       <c r="O10">
-        <v>59.90174192000001</v>
+        <v>59.72195966000001</v>
       </c>
       <c r="P10">
-        <v>139.7707311466667</v>
+        <v>139.3512392066667</v>
       </c>
       <c r="Q10">
-        <v>223.9707311466667</v>
+        <v>223.5512392066667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1061519630340477</v>
+        <v>0.1066276247855771</v>
       </c>
       <c r="T10">
-        <v>0.8781945987758055</v>
+        <v>0.8851160568367749</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.64881306976562</v>
+        <v>37.91005606201389</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1002000385548752</v>
+        <v>0.09992347111842642</v>
       </c>
       <c r="C11">
-        <v>1005.74378367376</v>
+        <v>999.1618467716888</v>
       </c>
       <c r="D11">
-        <v>1043.46978367376</v>
+        <v>1048.801846771689</v>
       </c>
       <c r="E11">
-        <v>-576.974</v>
+        <v>-565.0600000000001</v>
       </c>
       <c r="F11">
-        <v>107.226</v>
+        <v>119.14</v>
       </c>
       <c r="G11">
         <v>69.5</v>
@@ -2195,28 +2195,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M11">
-        <v>5.3934678</v>
+        <v>5.992742</v>
       </c>
       <c r="N11">
-        <v>199.0731988666667</v>
+        <v>198.4739246666667</v>
       </c>
       <c r="O11">
-        <v>59.72195966000001</v>
+        <v>59.54217740000001</v>
       </c>
       <c r="P11">
-        <v>139.3512392066667</v>
+        <v>138.9317472666667</v>
       </c>
       <c r="Q11">
-        <v>223.5512392066667</v>
+        <v>223.1317472666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1066276247855771</v>
+        <v>0.1071138567982516</v>
       </c>
       <c r="T11">
-        <v>0.8851160568367749</v>
+        <v>0.8921913250768769</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.91005606201389</v>
+        <v>34.1190504558125</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09992347111842642</v>
+        <v>0.09964690368197769</v>
       </c>
       <c r="C12">
-        <v>999.1618467716888</v>
+        <v>992.6346827505498</v>
       </c>
       <c r="D12">
-        <v>1048.801846771689</v>
+        <v>1054.18868275055</v>
       </c>
       <c r="E12">
-        <v>-565.0600000000001</v>
+        <v>-553.1460000000001</v>
       </c>
       <c r="F12">
-        <v>119.14</v>
+        <v>131.054</v>
       </c>
       <c r="G12">
         <v>69.5</v>
@@ -2277,28 +2277,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M12">
-        <v>5.992742000000001</v>
+        <v>6.5920162</v>
       </c>
       <c r="N12">
-        <v>198.4739246666667</v>
+        <v>197.8746504666667</v>
       </c>
       <c r="O12">
-        <v>59.54217740000001</v>
+        <v>59.36239514000001</v>
       </c>
       <c r="P12">
-        <v>138.9317472666667</v>
+        <v>138.5122553266667</v>
       </c>
       <c r="Q12">
-        <v>223.1317472666667</v>
+        <v>222.7122553266667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1071138567982516</v>
+        <v>0.1076110153730086</v>
       </c>
       <c r="T12">
-        <v>0.8921913250768769</v>
+        <v>0.8994255881088915</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.11905045581249</v>
+        <v>31.01731859619318</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09964690368197769</v>
+        <v>0.09937033624552893</v>
       </c>
       <c r="C13">
-        <v>992.6346827505498</v>
+        <v>986.1631399377761</v>
       </c>
       <c r="D13">
-        <v>1054.18868275055</v>
+        <v>1059.631139937776</v>
       </c>
       <c r="E13">
-        <v>-553.1460000000001</v>
+        <v>-541.232</v>
       </c>
       <c r="F13">
-        <v>131.054</v>
+        <v>142.968</v>
       </c>
       <c r="G13">
         <v>69.5</v>
@@ -2359,28 +2359,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M13">
-        <v>6.5920162</v>
+        <v>7.191290400000001</v>
       </c>
       <c r="N13">
-        <v>197.8746504666667</v>
+        <v>197.2753762666667</v>
       </c>
       <c r="O13">
-        <v>59.36239514000001</v>
+        <v>59.18261288</v>
       </c>
       <c r="P13">
-        <v>138.5122553266667</v>
+        <v>138.0927633866667</v>
       </c>
       <c r="Q13">
-        <v>222.7122553266667</v>
+        <v>222.2927633866667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1076110153730086</v>
+        <v>0.1081194730062829</v>
       </c>
       <c r="T13">
-        <v>0.8994255881088915</v>
+        <v>0.9068242662098155</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.01731859619318</v>
+        <v>28.43254204651041</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09937033624552893</v>
+        <v>0.0990937688090802</v>
       </c>
       <c r="C14">
-        <v>986.1631399377761</v>
+        <v>979.7480842703435</v>
       </c>
       <c r="D14">
-        <v>1059.631139937776</v>
+        <v>1065.130084270344</v>
       </c>
       <c r="E14">
-        <v>-541.232</v>
+        <v>-529.318</v>
       </c>
       <c r="F14">
-        <v>142.968</v>
+        <v>154.882</v>
       </c>
       <c r="G14">
         <v>69.5</v>
@@ -2441,28 +2441,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M14">
-        <v>7.191290400000001</v>
+        <v>7.7905646</v>
       </c>
       <c r="N14">
-        <v>197.2753762666667</v>
+        <v>196.6761020666667</v>
       </c>
       <c r="O14">
-        <v>59.18261288</v>
+        <v>59.00283062</v>
       </c>
       <c r="P14">
-        <v>138.0927633866667</v>
+        <v>137.6732714466667</v>
       </c>
       <c r="Q14">
-        <v>222.2927633866667</v>
+        <v>221.8732714466667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1081194730062829</v>
+        <v>0.1086396193207818</v>
       </c>
       <c r="T14">
-        <v>0.9068242662098155</v>
+        <v>0.9143930288647836</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.43254204651041</v>
+        <v>26.24542342754808</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0990937688090802</v>
+        <v>0.09881720137263145</v>
       </c>
       <c r="C15">
-        <v>979.7480842703435</v>
+        <v>973.3903997540792</v>
       </c>
       <c r="D15">
-        <v>1065.130084270344</v>
+        <v>1070.686399754079</v>
       </c>
       <c r="E15">
-        <v>-529.318</v>
+        <v>-517.404</v>
       </c>
       <c r="F15">
-        <v>154.882</v>
+        <v>166.796</v>
       </c>
       <c r="G15">
         <v>69.5</v>
@@ -2523,28 +2523,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M15">
-        <v>7.7905646</v>
+        <v>8.389838800000001</v>
       </c>
       <c r="N15">
-        <v>196.6761020666667</v>
+        <v>196.0768278666667</v>
       </c>
       <c r="O15">
-        <v>59.00283062</v>
+        <v>58.82304836</v>
       </c>
       <c r="P15">
-        <v>137.6732714466667</v>
+        <v>137.2537795066667</v>
       </c>
       <c r="Q15">
-        <v>221.8732714466667</v>
+        <v>221.4537795066667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1086396193207818</v>
+        <v>0.1091718620611994</v>
       </c>
       <c r="T15">
-        <v>0.9143930288647836</v>
+        <v>0.9221378092559138</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.24542342754808</v>
+        <v>24.37075032558035</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09881720137263145</v>
+        <v>0.09854063393618272</v>
       </c>
       <c r="C16">
-        <v>973.3903997540792</v>
+        <v>967.0909889374177</v>
       </c>
       <c r="D16">
-        <v>1070.686399754079</v>
+        <v>1076.300988937418</v>
       </c>
       <c r="E16">
-        <v>-517.404</v>
+        <v>-505.49</v>
       </c>
       <c r="F16">
-        <v>166.796</v>
+        <v>178.71</v>
       </c>
       <c r="G16">
         <v>69.5</v>
@@ -2605,28 +2605,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M16">
-        <v>8.389838800000001</v>
+        <v>8.989113000000001</v>
       </c>
       <c r="N16">
-        <v>196.0768278666667</v>
+        <v>195.4775536666667</v>
       </c>
       <c r="O16">
-        <v>58.82304836</v>
+        <v>58.64326610000001</v>
       </c>
       <c r="P16">
-        <v>137.2537795066667</v>
+        <v>136.8342875666667</v>
       </c>
       <c r="Q16">
-        <v>221.4537795066667</v>
+        <v>221.0342875666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1091718620611994</v>
+        <v>0.109716628160215</v>
       </c>
       <c r="T16">
-        <v>0.9221378092559138</v>
+        <v>0.9300648197738942</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.37075032558035</v>
+        <v>22.74603363720833</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09854063393618272</v>
+        <v>0.09826406649973397</v>
       </c>
       <c r="C17">
-        <v>967.0909889374177</v>
+        <v>960.8507734001448</v>
       </c>
       <c r="D17">
-        <v>1076.300988937418</v>
+        <v>1081.974773400145</v>
       </c>
       <c r="E17">
-        <v>-505.49</v>
+        <v>-493.576</v>
       </c>
       <c r="F17">
-        <v>178.71</v>
+        <v>190.624</v>
       </c>
       <c r="G17">
         <v>69.5</v>
@@ -2687,28 +2687,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M17">
-        <v>8.989113</v>
+        <v>9.588387200000001</v>
       </c>
       <c r="N17">
-        <v>195.4775536666667</v>
+        <v>194.8782794666667</v>
       </c>
       <c r="O17">
-        <v>58.64326610000001</v>
+        <v>58.46348384000001</v>
       </c>
       <c r="P17">
-        <v>136.8342875666667</v>
+        <v>136.4147956266667</v>
       </c>
       <c r="Q17">
-        <v>221.0342875666667</v>
+        <v>220.6147956266667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.109716628160215</v>
+        <v>0.1102743648806357</v>
       </c>
       <c r="T17">
-        <v>0.9300648197738942</v>
+        <v>0.9381805686375407</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.74603363720833</v>
+        <v>21.32440653488281</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09826406649973397</v>
+        <v>0.09798749906328523</v>
       </c>
       <c r="C18">
-        <v>960.8507734001448</v>
+        <v>954.6706942576784</v>
       </c>
       <c r="D18">
-        <v>1081.974773400145</v>
+        <v>1087.708694257678</v>
       </c>
       <c r="E18">
-        <v>-493.576</v>
+        <v>-481.662</v>
       </c>
       <c r="F18">
-        <v>190.624</v>
+        <v>202.538</v>
       </c>
       <c r="G18">
         <v>69.5</v>
@@ -2769,28 +2769,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M18">
-        <v>9.588387200000001</v>
+        <v>10.1876614</v>
       </c>
       <c r="N18">
-        <v>194.8782794666667</v>
+        <v>194.2790052666667</v>
       </c>
       <c r="O18">
-        <v>58.46348384000001</v>
+        <v>58.28370158000001</v>
       </c>
       <c r="P18">
-        <v>136.4147956266667</v>
+        <v>135.9953036866667</v>
       </c>
       <c r="Q18">
-        <v>220.6147956266667</v>
+        <v>220.1953036866667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1102743648806357</v>
+        <v>0.1108455410401027</v>
       </c>
       <c r="T18">
-        <v>0.9381805686375407</v>
+        <v>0.9464918777147693</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.32440653488281</v>
+        <v>20.0700296798897</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09798749906328523</v>
+        <v>0.09771093162683649</v>
       </c>
       <c r="C19">
-        <v>954.6706942576784</v>
+        <v>948.551712681473</v>
       </c>
       <c r="D19">
-        <v>1087.708694257678</v>
+        <v>1093.503712681473</v>
       </c>
       <c r="E19">
-        <v>-481.662</v>
+        <v>-469.748</v>
       </c>
       <c r="F19">
-        <v>202.538</v>
+        <v>214.4520000000001</v>
       </c>
       <c r="G19">
         <v>69.5</v>
@@ -2851,28 +2851,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M19">
-        <v>10.1876614</v>
+        <v>10.7869356</v>
       </c>
       <c r="N19">
-        <v>194.2790052666667</v>
+        <v>193.6797310666667</v>
       </c>
       <c r="O19">
-        <v>58.28370158000001</v>
+        <v>58.10391932000001</v>
       </c>
       <c r="P19">
-        <v>135.9953036866667</v>
+        <v>135.5758117466667</v>
       </c>
       <c r="Q19">
-        <v>220.1953036866667</v>
+        <v>219.7758117466667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1108455410401027</v>
+        <v>0.1114306483254104</v>
       </c>
       <c r="T19">
-        <v>0.9464918777147693</v>
+        <v>0.9550059016475396</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.0700296798897</v>
+        <v>18.95502803100694</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0977109316268365</v>
+        <v>0.09743436419038776</v>
       </c>
       <c r="C20">
-        <v>948.5517126814727</v>
+        <v>942.4948104361461</v>
       </c>
       <c r="D20">
-        <v>1093.503712681473</v>
+        <v>1099.360810436146</v>
       </c>
       <c r="E20">
-        <v>-469.748</v>
+        <v>-457.8340000000001</v>
       </c>
       <c r="F20">
-        <v>214.452</v>
+        <v>226.366</v>
       </c>
       <c r="G20">
         <v>69.5</v>
@@ -2933,28 +2933,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M20">
-        <v>10.7869356</v>
+        <v>11.3862098</v>
       </c>
       <c r="N20">
-        <v>193.6797310666667</v>
+        <v>193.0804568666667</v>
       </c>
       <c r="O20">
-        <v>58.10391932000001</v>
+        <v>57.92413706000001</v>
       </c>
       <c r="P20">
-        <v>135.5758117466667</v>
+        <v>135.1563198066667</v>
       </c>
       <c r="Q20">
-        <v>219.7758117466667</v>
+        <v>219.3563198066667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1114306483254104</v>
+        <v>0.1120302027041824</v>
       </c>
       <c r="T20">
-        <v>0.9550059016475396</v>
+        <v>0.9637301483934649</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.95502803100694</v>
+        <v>17.95739497674342</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09743436419038776</v>
+        <v>0.09715779675393901</v>
       </c>
       <c r="C21">
-        <v>942.4948104361461</v>
+        <v>936.5009904339613</v>
       </c>
       <c r="D21">
-        <v>1099.360810436146</v>
+        <v>1105.280990433961</v>
       </c>
       <c r="E21">
-        <v>-457.8340000000001</v>
+        <v>-445.92</v>
       </c>
       <c r="F21">
-        <v>226.366</v>
+        <v>238.28</v>
       </c>
       <c r="G21">
         <v>69.5</v>
@@ -3015,28 +3015,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M21">
-        <v>11.3862098</v>
+        <v>11.985484</v>
       </c>
       <c r="N21">
-        <v>193.0804568666667</v>
+        <v>192.4811826666667</v>
       </c>
       <c r="O21">
-        <v>57.92413706000001</v>
+        <v>57.7443548</v>
       </c>
       <c r="P21">
-        <v>135.1563198066667</v>
+        <v>134.7368278666667</v>
       </c>
       <c r="Q21">
-        <v>219.3563198066667</v>
+        <v>218.9368278666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1120302027041824</v>
+        <v>0.1126447459424238</v>
       </c>
       <c r="T21">
-        <v>0.9637301483934649</v>
+        <v>0.9726725013080386</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.95739497674342</v>
+        <v>17.05952522790625</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09715779675393901</v>
+        <v>0.09688122931749027</v>
       </c>
       <c r="C22">
-        <v>936.5009904339613</v>
+        <v>930.5712773073232</v>
       </c>
       <c r="D22">
-        <v>1105.280990433961</v>
+        <v>1111.265277307323</v>
       </c>
       <c r="E22">
-        <v>-445.92</v>
+        <v>-434.006</v>
       </c>
       <c r="F22">
-        <v>238.28</v>
+        <v>250.194</v>
       </c>
       <c r="G22">
         <v>69.5</v>
@@ -3097,28 +3097,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M22">
-        <v>11.985484</v>
+        <v>12.5847582</v>
       </c>
       <c r="N22">
-        <v>192.4811826666667</v>
+        <v>191.8819084666667</v>
       </c>
       <c r="O22">
-        <v>57.7443548</v>
+        <v>57.56457254000001</v>
       </c>
       <c r="P22">
-        <v>134.7368278666667</v>
+        <v>134.3173359266667</v>
       </c>
       <c r="Q22">
-        <v>218.9368278666667</v>
+        <v>218.5173359266667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1126447459424238</v>
+        <v>0.1132748472373294</v>
       </c>
       <c r="T22">
-        <v>0.9726725013080386</v>
+        <v>0.9818412429039938</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.05952522790625</v>
+        <v>16.24716688372023</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09688122931749027</v>
+        <v>0.09660466188104153</v>
       </c>
       <c r="C23">
-        <v>930.5712773073233</v>
+        <v>924.7067179999713</v>
       </c>
       <c r="D23">
-        <v>1111.265277307323</v>
+        <v>1117.314717999971</v>
       </c>
       <c r="E23">
-        <v>-434.006</v>
+        <v>-422.092</v>
       </c>
       <c r="F23">
-        <v>250.194</v>
+        <v>262.108</v>
       </c>
       <c r="G23">
         <v>69.5</v>
@@ -3179,28 +3179,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M23">
-        <v>12.5847582</v>
+        <v>13.1840324</v>
       </c>
       <c r="N23">
-        <v>191.8819084666667</v>
+        <v>191.2826342666667</v>
       </c>
       <c r="O23">
-        <v>57.56457254000001</v>
+        <v>57.38479028</v>
       </c>
       <c r="P23">
-        <v>134.3173359266667</v>
+        <v>133.8978439866667</v>
       </c>
       <c r="Q23">
-        <v>218.5173359266667</v>
+        <v>218.0978439866667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1132748472373294</v>
+        <v>0.1139211049756943</v>
       </c>
       <c r="T23">
-        <v>0.9818412429039937</v>
+        <v>0.9912450804383066</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.24716688372024</v>
+        <v>15.50865929809659</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09660466188104153</v>
+        <v>0.09632809444459278</v>
       </c>
       <c r="C24">
-        <v>924.7067179999713</v>
+        <v>918.908382377589</v>
       </c>
       <c r="D24">
-        <v>1117.314717999971</v>
+        <v>1123.430382377589</v>
       </c>
       <c r="E24">
-        <v>-422.092</v>
+        <v>-410.178</v>
       </c>
       <c r="F24">
-        <v>262.108</v>
+        <v>274.022</v>
       </c>
       <c r="G24">
         <v>69.5</v>
@@ -3261,28 +3261,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M24">
-        <v>13.1840324</v>
+        <v>13.7833066</v>
       </c>
       <c r="N24">
-        <v>191.2826342666667</v>
+        <v>190.6833600666667</v>
       </c>
       <c r="O24">
-        <v>57.38479028</v>
+        <v>57.20500802000001</v>
       </c>
       <c r="P24">
-        <v>133.8978439866667</v>
+        <v>133.4783520466667</v>
       </c>
       <c r="Q24">
-        <v>218.0978439866667</v>
+        <v>217.6783520466667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1139211049756943</v>
+        <v>0.1145841486293413</v>
       </c>
       <c r="T24">
-        <v>0.9912450804383066</v>
+        <v>1.000893173492991</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.50865929809659</v>
+        <v>14.83436976339674</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09632809444459278</v>
+        <v>0.09605152700814404</v>
       </c>
       <c r="C25">
-        <v>918.908382377589</v>
+        <v>913.1773638585784</v>
       </c>
       <c r="D25">
-        <v>1123.430382377589</v>
+        <v>1129.613363858578</v>
       </c>
       <c r="E25">
-        <v>-410.178</v>
+        <v>-398.264</v>
       </c>
       <c r="F25">
-        <v>274.022</v>
+        <v>285.936</v>
       </c>
       <c r="G25">
         <v>69.5</v>
@@ -3343,28 +3343,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M25">
-        <v>13.7833066</v>
+        <v>14.3825808</v>
       </c>
       <c r="N25">
-        <v>190.6833600666667</v>
+        <v>190.0840858666667</v>
       </c>
       <c r="O25">
-        <v>57.20500802000001</v>
+        <v>57.02522576</v>
       </c>
       <c r="P25">
-        <v>133.4783520466667</v>
+        <v>133.0588601066667</v>
       </c>
       <c r="Q25">
-        <v>217.6783520466667</v>
+        <v>217.2588601066667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1145841486293413</v>
+        <v>0.1152646408001895</v>
       </c>
       <c r="T25">
-        <v>1.000893173492991</v>
+        <v>1.010795163733326</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.83436976339674</v>
+        <v>14.21627102325521</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09605152700814404</v>
+        <v>0.09577495957169531</v>
       </c>
       <c r="C26">
-        <v>913.1773638585784</v>
+        <v>907.514780065777</v>
       </c>
       <c r="D26">
-        <v>1129.613363858578</v>
+        <v>1135.864780065777</v>
       </c>
       <c r="E26">
-        <v>-398.264</v>
+        <v>-386.35</v>
       </c>
       <c r="F26">
-        <v>285.936</v>
+        <v>297.85</v>
       </c>
       <c r="G26">
         <v>69.5</v>
@@ -3425,28 +3425,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M26">
-        <v>14.3825808</v>
+        <v>14.981855</v>
       </c>
       <c r="N26">
-        <v>190.0840858666667</v>
+        <v>189.4848116666667</v>
       </c>
       <c r="O26">
-        <v>57.02522576</v>
+        <v>56.84544350000001</v>
       </c>
       <c r="P26">
-        <v>133.0588601066667</v>
+        <v>132.6393681666667</v>
       </c>
       <c r="Q26">
-        <v>217.2588601066667</v>
+        <v>216.8393681666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1152646408001895</v>
+        <v>0.1159632794289271</v>
       </c>
       <c r="T26">
-        <v>1.010795163733326</v>
+        <v>1.020961207046736</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.21627102325521</v>
+        <v>13.647620182325</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09577495957169531</v>
+        <v>0.09549839213524655</v>
       </c>
       <c r="C27">
-        <v>907.514780065777</v>
+        <v>901.9217734999376</v>
       </c>
       <c r="D27">
-        <v>1135.864780065777</v>
+        <v>1142.185773499938</v>
       </c>
       <c r="E27">
-        <v>-386.35</v>
+        <v>-374.436</v>
       </c>
       <c r="F27">
-        <v>297.85</v>
+        <v>309.764</v>
       </c>
       <c r="G27">
         <v>69.5</v>
@@ -3507,28 +3507,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M27">
-        <v>14.981855</v>
+        <v>15.5811292</v>
       </c>
       <c r="N27">
-        <v>189.4848116666667</v>
+        <v>188.8855374666667</v>
       </c>
       <c r="O27">
-        <v>56.84544350000001</v>
+        <v>56.66566124000001</v>
       </c>
       <c r="P27">
-        <v>132.6393681666667</v>
+        <v>132.2198762266667</v>
       </c>
       <c r="Q27">
-        <v>216.8393681666667</v>
+        <v>216.4198762266667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1159632794289271</v>
+        <v>0.1166808001827656</v>
       </c>
       <c r="T27">
-        <v>1.020961207046736</v>
+        <v>1.031402008287535</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.647620182325</v>
+        <v>13.12271171377404</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09549839213524655</v>
+        <v>0.09550532469879781</v>
       </c>
       <c r="C28">
-        <v>901.9217734999376</v>
+        <v>889.8484691294275</v>
       </c>
       <c r="D28">
-        <v>1142.185773499938</v>
+        <v>1142.026469129428</v>
       </c>
       <c r="E28">
-        <v>-374.436</v>
+        <v>-362.522</v>
       </c>
       <c r="F28">
-        <v>309.764</v>
+        <v>321.6780000000001</v>
       </c>
       <c r="G28">
         <v>69.5</v>
@@ -3589,45 +3589,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M28">
-        <v>15.5811292</v>
+        <v>16.6629204</v>
       </c>
       <c r="N28">
-        <v>188.8855374666667</v>
+        <v>187.8037462666667</v>
       </c>
       <c r="O28">
-        <v>56.66566124000001</v>
+        <v>56.34112388000001</v>
       </c>
       <c r="P28">
-        <v>132.2198762266667</v>
+        <v>131.4626223866667</v>
       </c>
       <c r="Q28">
-        <v>216.4198762266667</v>
+        <v>215.6626223866667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1166808001827656</v>
+        <v>0.1174179790394491</v>
       </c>
       <c r="T28">
-        <v>1.031402008287535</v>
+        <v>1.042128858877397</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.12271171377404</v>
+        <v>12.27075817193886</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09550532469879781</v>
+        <v>0.09523925726234907</v>
       </c>
       <c r="C29">
-        <v>889.8484691294275</v>
+        <v>884.0805172665478</v>
       </c>
       <c r="D29">
-        <v>1142.026469129428</v>
+        <v>1148.172517266548</v>
       </c>
       <c r="E29">
-        <v>-362.522</v>
+        <v>-350.608</v>
       </c>
       <c r="F29">
-        <v>321.6780000000001</v>
+        <v>333.592</v>
       </c>
       <c r="G29">
         <v>69.5</v>
@@ -3671,28 +3671,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M29">
-        <v>16.6629204</v>
+        <v>17.2800656</v>
       </c>
       <c r="N29">
-        <v>187.8037462666667</v>
+        <v>187.1866010666667</v>
       </c>
       <c r="O29">
-        <v>56.34112388000001</v>
+        <v>56.15598032</v>
       </c>
       <c r="P29">
-        <v>131.4626223866667</v>
+        <v>131.0306207466667</v>
       </c>
       <c r="Q29">
-        <v>215.6626223866667</v>
+        <v>215.2306207466667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1174179790394491</v>
+        <v>0.1181756350865959</v>
       </c>
       <c r="T29">
-        <v>1.042128858877397</v>
+        <v>1.0531536775392</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.27075817193886</v>
+        <v>11.83251680865533</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09523925726234907</v>
+        <v>0.09497318982590032</v>
       </c>
       <c r="C30">
-        <v>884.0805172665478</v>
+        <v>878.379075763396</v>
       </c>
       <c r="D30">
-        <v>1148.172517266548</v>
+        <v>1154.385075763396</v>
       </c>
       <c r="E30">
-        <v>-350.608</v>
+        <v>-338.694</v>
       </c>
       <c r="F30">
-        <v>333.592</v>
+        <v>345.5060000000001</v>
       </c>
       <c r="G30">
         <v>69.5</v>
@@ -3753,28 +3753,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M30">
-        <v>17.2800656</v>
+        <v>17.8972108</v>
       </c>
       <c r="N30">
-        <v>187.1866010666667</v>
+        <v>186.5694558666667</v>
       </c>
       <c r="O30">
-        <v>56.15598032</v>
+        <v>55.97083676</v>
       </c>
       <c r="P30">
-        <v>131.0306207466667</v>
+        <v>130.5986191066667</v>
       </c>
       <c r="Q30">
-        <v>215.2306207466667</v>
+        <v>214.7986191066667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1181756350865959</v>
+        <v>0.1189546335576061</v>
       </c>
       <c r="T30">
-        <v>1.0531536775392</v>
+        <v>1.064489054473167</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.83251680865533</v>
+        <v>11.42449898766721</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09497318982590032</v>
+        <v>0.0947071223894516</v>
       </c>
       <c r="C31">
-        <v>878.379075763396</v>
+        <v>872.7452301208168</v>
       </c>
       <c r="D31">
-        <v>1154.385075763396</v>
+        <v>1160.665230120817</v>
       </c>
       <c r="E31">
-        <v>-338.694</v>
+        <v>-326.78</v>
       </c>
       <c r="F31">
-        <v>345.506</v>
+        <v>357.42</v>
       </c>
       <c r="G31">
         <v>69.5</v>
@@ -3835,28 +3835,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M31">
-        <v>17.8972108</v>
+        <v>18.514356</v>
       </c>
       <c r="N31">
-        <v>186.5694558666667</v>
+        <v>185.9523106666667</v>
       </c>
       <c r="O31">
-        <v>55.97083676</v>
+        <v>55.78569320000001</v>
       </c>
       <c r="P31">
-        <v>130.5986191066667</v>
+        <v>130.1666174666667</v>
       </c>
       <c r="Q31">
-        <v>214.7986191066667</v>
+        <v>214.3666174666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1189546335576061</v>
+        <v>0.119755889127788</v>
       </c>
       <c r="T31">
-        <v>1.064489054473167</v>
+        <v>1.076148299319532</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.42449898766721</v>
+        <v>11.04368235474497</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0947071223894516</v>
+        <v>0.09444105495300284</v>
       </c>
       <c r="C32">
-        <v>872.7452301208168</v>
+        <v>867.1800895904939</v>
       </c>
       <c r="D32">
-        <v>1160.665230120817</v>
+        <v>1167.014089590494</v>
       </c>
       <c r="E32">
-        <v>-326.78</v>
+        <v>-314.866</v>
       </c>
       <c r="F32">
-        <v>357.42</v>
+        <v>369.334</v>
       </c>
       <c r="G32">
         <v>69.5</v>
@@ -3917,28 +3917,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M32">
-        <v>18.514356</v>
+        <v>19.1315012</v>
       </c>
       <c r="N32">
-        <v>185.9523106666667</v>
+        <v>185.3351654666667</v>
       </c>
       <c r="O32">
-        <v>55.78569320000001</v>
+        <v>55.60054964</v>
       </c>
       <c r="P32">
-        <v>130.1666174666667</v>
+        <v>129.7346158266667</v>
       </c>
       <c r="Q32">
-        <v>214.3666174666667</v>
+        <v>213.9346158266667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.119755889127788</v>
+        <v>0.1205803694971056</v>
       </c>
       <c r="T32">
-        <v>1.076148299319532</v>
+        <v>1.088145493291879</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.04368235474497</v>
+        <v>10.68743453684997</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09444105495300284</v>
+        <v>0.09417498751655409</v>
       </c>
       <c r="C33">
-        <v>867.1800895904939</v>
+        <v>861.6847878281039</v>
       </c>
       <c r="D33">
-        <v>1167.014089590494</v>
+        <v>1173.432787828104</v>
       </c>
       <c r="E33">
-        <v>-314.866</v>
+        <v>-302.952</v>
       </c>
       <c r="F33">
-        <v>369.334</v>
+        <v>381.248</v>
       </c>
       <c r="G33">
         <v>69.5</v>
@@ -3999,28 +3999,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M33">
-        <v>19.1315012</v>
+        <v>19.7486464</v>
       </c>
       <c r="N33">
-        <v>185.3351654666667</v>
+        <v>184.7180202666667</v>
       </c>
       <c r="O33">
-        <v>55.60054964</v>
+        <v>55.41540608</v>
       </c>
       <c r="P33">
-        <v>129.7346158266667</v>
+        <v>129.3026141866667</v>
       </c>
       <c r="Q33">
-        <v>213.9346158266667</v>
+        <v>213.5026141866667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1205803694971056</v>
+        <v>0.1214290992890502</v>
       </c>
       <c r="T33">
-        <v>1.088145493291879</v>
+        <v>1.100495545910472</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.68743453684997</v>
+        <v>10.35345220757341</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09417498751655409</v>
+        <v>0.09390892008010536</v>
       </c>
       <c r="C34">
-        <v>861.6847878281039</v>
+        <v>856.2604835681548</v>
       </c>
       <c r="D34">
-        <v>1173.432787828104</v>
+        <v>1179.922483568155</v>
       </c>
       <c r="E34">
-        <v>-302.952</v>
+        <v>-291.038</v>
       </c>
       <c r="F34">
-        <v>381.248</v>
+        <v>393.162</v>
       </c>
       <c r="G34">
         <v>69.5</v>
@@ -4081,28 +4081,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M34">
-        <v>19.7486464</v>
+        <v>20.3657916</v>
       </c>
       <c r="N34">
-        <v>184.7180202666667</v>
+        <v>184.1008750666667</v>
       </c>
       <c r="O34">
-        <v>55.41540608</v>
+        <v>55.23026252000001</v>
       </c>
       <c r="P34">
-        <v>129.3026141866667</v>
+        <v>128.8706125466667</v>
       </c>
       <c r="Q34">
-        <v>213.5026141866667</v>
+        <v>213.0706125466667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1214290992890502</v>
+        <v>0.1223031642986647</v>
       </c>
       <c r="T34">
-        <v>1.100495545910472</v>
+        <v>1.113214256816186</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.35345220757341</v>
+        <v>10.03971123158634</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09390892008010536</v>
+        <v>0.0940474526436566</v>
       </c>
       <c r="C35">
-        <v>856.2604835681548</v>
+        <v>840.9585806326841</v>
       </c>
       <c r="D35">
-        <v>1179.922483568155</v>
+        <v>1176.534580632684</v>
       </c>
       <c r="E35">
-        <v>-291.038</v>
+        <v>-279.124</v>
       </c>
       <c r="F35">
-        <v>393.162</v>
+        <v>405.0760000000001</v>
       </c>
       <c r="G35">
         <v>69.5</v>
@@ -4163,45 +4163,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M35">
-        <v>20.3657916</v>
+        <v>21.671566</v>
       </c>
       <c r="N35">
-        <v>184.1008750666667</v>
+        <v>182.7951006666667</v>
       </c>
       <c r="O35">
-        <v>55.23026252000001</v>
+        <v>54.8385302</v>
       </c>
       <c r="P35">
-        <v>128.8706125466667</v>
+        <v>127.9565704666667</v>
       </c>
       <c r="Q35">
-        <v>213.0706125466667</v>
+        <v>212.1565704666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1223031642986647</v>
+        <v>0.1232037161267525</v>
       </c>
       <c r="T35">
-        <v>1.113214256816186</v>
+        <v>1.126318383203893</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>10.03971123158634</v>
+        <v>9.43478965325656</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0940474526436566</v>
+        <v>0.09379328520720787</v>
       </c>
       <c r="C36">
-        <v>840.9585806326841</v>
+        <v>835.2753851496414</v>
       </c>
       <c r="D36">
-        <v>1176.534580632684</v>
+        <v>1182.765385149641</v>
       </c>
       <c r="E36">
-        <v>-279.124</v>
+        <v>-267.21</v>
       </c>
       <c r="F36">
-        <v>405.0760000000001</v>
+        <v>416.9900000000001</v>
       </c>
       <c r="G36">
         <v>69.5</v>
@@ -4245,28 +4245,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M36">
-        <v>21.671566</v>
+        <v>22.308965</v>
       </c>
       <c r="N36">
-        <v>182.7951006666667</v>
+        <v>182.1577016666667</v>
       </c>
       <c r="O36">
-        <v>54.8385302</v>
+        <v>54.64731050000001</v>
       </c>
       <c r="P36">
-        <v>127.9565704666667</v>
+        <v>127.5103911666667</v>
       </c>
       <c r="Q36">
-        <v>212.1565704666667</v>
+        <v>211.7103911666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1232037161267525</v>
+        <v>0.1241319772418583</v>
       </c>
       <c r="T36">
-        <v>1.126318383203893</v>
+        <v>1.139825713480451</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.43478965325656</v>
+        <v>9.165224234592086</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09379328520720787</v>
+        <v>0.09353911777075913</v>
       </c>
       <c r="C37">
-        <v>835.2753851496414</v>
+        <v>829.6585364147182</v>
       </c>
       <c r="D37">
-        <v>1182.765385149641</v>
+        <v>1189.062536414718</v>
       </c>
       <c r="E37">
-        <v>-267.21</v>
+        <v>-255.2959999999999</v>
       </c>
       <c r="F37">
-        <v>416.9900000000001</v>
+        <v>428.9040000000001</v>
       </c>
       <c r="G37">
         <v>69.5</v>
@@ -4327,28 +4327,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M37">
-        <v>22.308965</v>
+        <v>22.94636400000001</v>
       </c>
       <c r="N37">
-        <v>182.1577016666667</v>
+        <v>181.5203026666667</v>
       </c>
       <c r="O37">
-        <v>54.64731050000001</v>
+        <v>54.45609080000001</v>
       </c>
       <c r="P37">
-        <v>127.5103911666667</v>
+        <v>127.0642118666667</v>
       </c>
       <c r="Q37">
-        <v>211.7103911666667</v>
+        <v>211.2642118666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1241319772418583</v>
+        <v>0.1250892465168112</v>
       </c>
       <c r="T37">
-        <v>1.139825713480451</v>
+        <v>1.153755147828152</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.165224234592086</v>
+        <v>8.910634672520082</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09353911777075914</v>
+        <v>0.09328495033431039</v>
       </c>
       <c r="C38">
-        <v>829.6585364147179</v>
+        <v>824.109099808594</v>
       </c>
       <c r="D38">
-        <v>1189.062536414718</v>
+        <v>1195.427099808594</v>
       </c>
       <c r="E38">
-        <v>-255.296</v>
+        <v>-243.382</v>
       </c>
       <c r="F38">
-        <v>428.904</v>
+        <v>440.818</v>
       </c>
       <c r="G38">
         <v>69.5</v>
@@ -4409,28 +4409,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M38">
-        <v>22.946364</v>
+        <v>23.583763</v>
       </c>
       <c r="N38">
-        <v>181.5203026666667</v>
+        <v>180.8829036666667</v>
       </c>
       <c r="O38">
-        <v>54.45609080000001</v>
+        <v>54.26487110000001</v>
       </c>
       <c r="P38">
-        <v>127.0642118666667</v>
+        <v>126.6180325666667</v>
       </c>
       <c r="Q38">
-        <v>211.2642118666667</v>
+        <v>210.8180325666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1250892465168112</v>
+        <v>0.1260769052925562</v>
       </c>
       <c r="T38">
-        <v>1.153755147828152</v>
+        <v>1.16812678644086</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.910634672520086</v>
+        <v>8.669806708397921</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09328495033431039</v>
+        <v>0.09303078289786164</v>
       </c>
       <c r="C39">
-        <v>824.109099808594</v>
+        <v>818.62816364488</v>
       </c>
       <c r="D39">
-        <v>1195.427099808594</v>
+        <v>1201.86016364488</v>
       </c>
       <c r="E39">
-        <v>-243.382</v>
+        <v>-231.468</v>
       </c>
       <c r="F39">
-        <v>440.818</v>
+        <v>452.732</v>
       </c>
       <c r="G39">
         <v>69.5</v>
@@ -4491,28 +4491,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M39">
-        <v>23.583763</v>
+        <v>24.221162</v>
       </c>
       <c r="N39">
-        <v>180.8829036666667</v>
+        <v>180.2455046666667</v>
       </c>
       <c r="O39">
-        <v>54.26487110000001</v>
+        <v>54.07365140000001</v>
       </c>
       <c r="P39">
-        <v>126.6180325666667</v>
+        <v>126.1718532666667</v>
       </c>
       <c r="Q39">
-        <v>210.8180325666667</v>
+        <v>210.3718532666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1260769052925562</v>
+        <v>0.1270964240288091</v>
       </c>
       <c r="T39">
-        <v>1.16812678644086</v>
+        <v>1.182962026299138</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.669806708397921</v>
+        <v>8.441653900282187</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09303078289786164</v>
+        <v>0.0927766154614129</v>
       </c>
       <c r="C40">
-        <v>818.62816364488</v>
+        <v>813.2168397905126</v>
       </c>
       <c r="D40">
-        <v>1201.86016364488</v>
+        <v>1208.362839790513</v>
       </c>
       <c r="E40">
-        <v>-231.468</v>
+        <v>-219.554</v>
       </c>
       <c r="F40">
-        <v>452.732</v>
+        <v>464.6460000000001</v>
       </c>
       <c r="G40">
         <v>69.5</v>
@@ -4573,28 +4573,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M40">
-        <v>24.221162</v>
+        <v>24.858561</v>
       </c>
       <c r="N40">
-        <v>180.2455046666667</v>
+        <v>179.6081056666667</v>
       </c>
       <c r="O40">
-        <v>54.07365140000001</v>
+        <v>53.88243170000001</v>
       </c>
       <c r="P40">
-        <v>126.1718532666667</v>
+        <v>125.7256739666667</v>
       </c>
       <c r="Q40">
-        <v>210.3718532666667</v>
+        <v>209.9256739666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1270964240288091</v>
+        <v>0.1281493696088736</v>
       </c>
       <c r="T40">
-        <v>1.182962026299138</v>
+        <v>1.198283667464246</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.441653900282187</v>
+        <v>8.225201236172387</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0927766154614129</v>
+        <v>0.09252244802496418</v>
       </c>
       <c r="C41">
-        <v>813.2168397905126</v>
+        <v>807.8762643063973</v>
       </c>
       <c r="D41">
-        <v>1208.362839790513</v>
+        <v>1214.936264306397</v>
       </c>
       <c r="E41">
-        <v>-219.554</v>
+        <v>-207.64</v>
       </c>
       <c r="F41">
-        <v>464.6460000000001</v>
+        <v>476.5600000000001</v>
       </c>
       <c r="G41">
         <v>69.5</v>
@@ -4655,28 +4655,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M41">
-        <v>24.858561</v>
+        <v>25.49596</v>
       </c>
       <c r="N41">
-        <v>179.6081056666667</v>
+        <v>178.9707066666667</v>
       </c>
       <c r="O41">
-        <v>53.88243170000001</v>
+        <v>53.69121200000001</v>
       </c>
       <c r="P41">
-        <v>125.7256739666667</v>
+        <v>125.2794946666667</v>
       </c>
       <c r="Q41">
-        <v>209.9256739666667</v>
+        <v>209.4794946666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1281493696088736</v>
+        <v>0.1292374133749403</v>
       </c>
       <c r="T41">
-        <v>1.198283667464246</v>
+        <v>1.214116030001523</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.225201236172387</v>
+        <v>8.019571205268075</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09252244802496418</v>
+        <v>0.09226828058851541</v>
       </c>
       <c r="C42">
-        <v>807.8762643063973</v>
+        <v>802.60759810908</v>
       </c>
       <c r="D42">
-        <v>1214.936264306397</v>
+        <v>1221.58159810908</v>
       </c>
       <c r="E42">
-        <v>-207.64</v>
+        <v>-195.726</v>
       </c>
       <c r="F42">
-        <v>476.5600000000001</v>
+        <v>488.474</v>
       </c>
       <c r="G42">
         <v>69.5</v>
@@ -4737,28 +4737,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M42">
-        <v>25.49596</v>
+        <v>26.133359</v>
       </c>
       <c r="N42">
-        <v>178.9707066666667</v>
+        <v>178.3333076666667</v>
       </c>
       <c r="O42">
-        <v>53.69121200000001</v>
+        <v>53.4999923</v>
       </c>
       <c r="P42">
-        <v>125.2794946666667</v>
+        <v>124.8333153666667</v>
       </c>
       <c r="Q42">
-        <v>209.4794946666667</v>
+        <v>209.0333153666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1292374133749403</v>
+        <v>0.1303623399805346</v>
       </c>
       <c r="T42">
-        <v>1.214116030001523</v>
+        <v>1.230485082794302</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.019571205268075</v>
+        <v>7.823971907578612</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09226828058851541</v>
+        <v>0.09201411315206667</v>
       </c>
       <c r="C43">
-        <v>802.60759810908</v>
+        <v>797.4120276542426</v>
       </c>
       <c r="D43">
-        <v>1221.58159810908</v>
+        <v>1228.300027654243</v>
       </c>
       <c r="E43">
-        <v>-195.726</v>
+        <v>-183.812</v>
       </c>
       <c r="F43">
-        <v>488.474</v>
+        <v>500.3880000000001</v>
       </c>
       <c r="G43">
         <v>69.5</v>
@@ -4819,28 +4819,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M43">
-        <v>26.133359</v>
+        <v>26.770758</v>
       </c>
       <c r="N43">
-        <v>178.3333076666667</v>
+        <v>177.6959086666667</v>
       </c>
       <c r="O43">
-        <v>53.4999923</v>
+        <v>53.3087726</v>
       </c>
       <c r="P43">
-        <v>124.8333153666667</v>
+        <v>124.3871360666667</v>
       </c>
       <c r="Q43">
-        <v>209.0333153666667</v>
+        <v>208.5871360666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1303623399805346</v>
+        <v>0.1315260571587357</v>
       </c>
       <c r="T43">
-        <v>1.230485082794302</v>
+        <v>1.247418585683383</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.823971907578612</v>
+        <v>7.637686862160073</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0920141131520667</v>
+        <v>0.09200074571561795</v>
       </c>
       <c r="C44">
-        <v>797.412027654242</v>
+        <v>785.8534163456007</v>
       </c>
       <c r="D44">
-        <v>1228.300027654242</v>
+        <v>1228.655416345601</v>
       </c>
       <c r="E44">
-        <v>-183.812</v>
+        <v>-171.898</v>
       </c>
       <c r="F44">
-        <v>500.388</v>
+        <v>512.302</v>
       </c>
       <c r="G44">
         <v>69.5</v>
@@ -4901,45 +4901,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M44">
-        <v>26.770758</v>
+        <v>27.8179986</v>
       </c>
       <c r="N44">
-        <v>177.6959086666667</v>
+        <v>176.6486680666667</v>
       </c>
       <c r="O44">
-        <v>53.3087726</v>
+        <v>52.99460042</v>
       </c>
       <c r="P44">
-        <v>124.3871360666667</v>
+        <v>123.6540676466667</v>
       </c>
       <c r="Q44">
-        <v>208.5871360666667</v>
+        <v>207.8540676466667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1315260571587357</v>
+        <v>0.132730606518628</v>
       </c>
       <c r="T44">
-        <v>1.247418585683383</v>
+        <v>1.264946246568573</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.637686862160074</v>
+        <v>7.350157342615822</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09200074571561795</v>
+        <v>0.09175217827916921</v>
       </c>
       <c r="C45">
-        <v>785.8534163456007</v>
+        <v>780.5855371293532</v>
       </c>
       <c r="D45">
-        <v>1228.655416345601</v>
+        <v>1235.301537129353</v>
       </c>
       <c r="E45">
-        <v>-171.898</v>
+        <v>-159.984</v>
       </c>
       <c r="F45">
-        <v>512.302</v>
+        <v>524.216</v>
       </c>
       <c r="G45">
         <v>69.5</v>
@@ -4983,28 +4983,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M45">
-        <v>27.8179986</v>
+        <v>28.4649288</v>
       </c>
       <c r="N45">
-        <v>176.6486680666667</v>
+        <v>176.0017378666667</v>
       </c>
       <c r="O45">
-        <v>52.99460042</v>
+        <v>52.80052136000001</v>
       </c>
       <c r="P45">
-        <v>123.6540676466667</v>
+        <v>123.2012165066667</v>
       </c>
       <c r="Q45">
-        <v>207.8540676466667</v>
+        <v>207.4012165066667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.132730606518628</v>
+        <v>0.1339781754985164</v>
       </c>
       <c r="T45">
-        <v>1.264946246568573</v>
+        <v>1.283099895342519</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.350157342615822</v>
+        <v>7.183108312101827</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09175217827916921</v>
+        <v>0.09150361084272048</v>
       </c>
       <c r="C46">
-        <v>780.5855371293532</v>
+        <v>775.3899501970227</v>
       </c>
       <c r="D46">
-        <v>1235.301537129353</v>
+        <v>1242.019950197023</v>
       </c>
       <c r="E46">
-        <v>-159.984</v>
+        <v>-148.0699999999999</v>
       </c>
       <c r="F46">
-        <v>524.216</v>
+        <v>536.1300000000001</v>
       </c>
       <c r="G46">
         <v>69.5</v>
@@ -5065,28 +5065,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M46">
-        <v>28.4649288</v>
+        <v>29.11185900000001</v>
       </c>
       <c r="N46">
-        <v>176.0017378666667</v>
+        <v>175.3548076666667</v>
       </c>
       <c r="O46">
-        <v>52.80052136000001</v>
+        <v>52.6064423</v>
       </c>
       <c r="P46">
-        <v>123.2012165066667</v>
+        <v>122.7483653666667</v>
       </c>
       <c r="Q46">
-        <v>207.4012165066667</v>
+        <v>206.9483653666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1339781754985164</v>
+        <v>0.1352711106231281</v>
       </c>
       <c r="T46">
-        <v>1.283099895342519</v>
+        <v>1.301913676799154</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.183108312101827</v>
+        <v>7.023483682944008</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09150361084272048</v>
+        <v>0.09125504340627173</v>
       </c>
       <c r="C47">
-        <v>775.3899501970227</v>
+        <v>770.2678415231251</v>
       </c>
       <c r="D47">
-        <v>1242.019950197023</v>
+        <v>1248.811841523125</v>
       </c>
       <c r="E47">
-        <v>-148.0699999999999</v>
+        <v>-136.1559999999999</v>
       </c>
       <c r="F47">
-        <v>536.1300000000001</v>
+        <v>548.0440000000001</v>
       </c>
       <c r="G47">
         <v>69.5</v>
@@ -5147,28 +5147,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M47">
-        <v>29.11185900000001</v>
+        <v>29.75878920000001</v>
       </c>
       <c r="N47">
-        <v>175.3548076666667</v>
+        <v>174.7078774666667</v>
       </c>
       <c r="O47">
-        <v>52.6064423</v>
+        <v>52.41236324000001</v>
       </c>
       <c r="P47">
-        <v>122.7483653666667</v>
+        <v>122.2955142266667</v>
       </c>
       <c r="Q47">
-        <v>206.9483653666667</v>
+        <v>206.4955142266667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1352711106231281</v>
+        <v>0.1366119322338365</v>
       </c>
       <c r="T47">
-        <v>1.301913676799154</v>
+        <v>1.321424264976405</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.023483682944008</v>
+        <v>6.870799255053921</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09125504340627173</v>
+        <v>0.09100647596982299</v>
       </c>
       <c r="C48">
-        <v>770.2678415231251</v>
+        <v>765.22042316646</v>
       </c>
       <c r="D48">
-        <v>1248.811841523125</v>
+        <v>1255.67842316646</v>
       </c>
       <c r="E48">
-        <v>-136.1559999999999</v>
+        <v>-124.242</v>
       </c>
       <c r="F48">
-        <v>548.0440000000001</v>
+        <v>559.9580000000001</v>
       </c>
       <c r="G48">
         <v>69.5</v>
@@ -5229,28 +5229,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M48">
-        <v>29.75878920000001</v>
+        <v>30.40571940000001</v>
       </c>
       <c r="N48">
-        <v>174.7078774666667</v>
+        <v>174.0609472666667</v>
       </c>
       <c r="O48">
-        <v>52.41236324000001</v>
+        <v>52.21828418</v>
       </c>
       <c r="P48">
-        <v>122.2955142266667</v>
+        <v>121.8426630866667</v>
       </c>
       <c r="Q48">
-        <v>206.4955142266667</v>
+        <v>206.0426630866667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1366119322338365</v>
+        <v>0.1380033508864585</v>
       </c>
       <c r="T48">
-        <v>1.321424264976405</v>
+        <v>1.341671101764119</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.870799255053921</v>
+        <v>6.724612036861284</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09100647596982299</v>
+        <v>0.09075790853337423</v>
       </c>
       <c r="C49">
-        <v>765.22042316646</v>
+        <v>760.2489339911974</v>
       </c>
       <c r="D49">
-        <v>1255.67842316646</v>
+        <v>1262.620933991197</v>
       </c>
       <c r="E49">
-        <v>-124.242</v>
+        <v>-112.328</v>
       </c>
       <c r="F49">
-        <v>559.9580000000001</v>
+        <v>571.8720000000001</v>
       </c>
       <c r="G49">
         <v>69.5</v>
@@ -5311,28 +5311,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M49">
-        <v>30.40571940000001</v>
+        <v>31.05264960000001</v>
       </c>
       <c r="N49">
-        <v>174.0609472666667</v>
+        <v>173.4140170666667</v>
       </c>
       <c r="O49">
-        <v>52.21828418</v>
+        <v>52.02420512000001</v>
       </c>
       <c r="P49">
-        <v>121.8426630866667</v>
+        <v>121.3898119466667</v>
       </c>
       <c r="Q49">
-        <v>206.0426630866667</v>
+        <v>205.5898119466667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1380033508864585</v>
+        <v>0.1394482856411043</v>
       </c>
       <c r="T49">
-        <v>1.341671101764119</v>
+        <v>1.362696663043668</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.724612036861284</v>
+        <v>6.584515952760007</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09075790853337423</v>
+        <v>0.0905093410969255</v>
       </c>
       <c r="C50">
-        <v>760.2489339911974</v>
+        <v>755.3546404120166</v>
       </c>
       <c r="D50">
-        <v>1262.620933991197</v>
+        <v>1269.640640412017</v>
       </c>
       <c r="E50">
-        <v>-112.328</v>
+        <v>-100.414</v>
       </c>
       <c r="F50">
-        <v>571.8720000000001</v>
+        <v>583.7860000000001</v>
       </c>
       <c r="G50">
         <v>69.5</v>
@@ -5393,28 +5393,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M50">
-        <v>31.05264960000001</v>
+        <v>31.6995798</v>
       </c>
       <c r="N50">
-        <v>173.4140170666667</v>
+        <v>172.7670868666667</v>
       </c>
       <c r="O50">
-        <v>52.02420512000001</v>
+        <v>51.83012606</v>
       </c>
       <c r="P50">
-        <v>121.3898119466667</v>
+        <v>120.9369608066667</v>
       </c>
       <c r="Q50">
-        <v>205.5898119466667</v>
+        <v>205.1369608066667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1394482856411043</v>
+        <v>0.1409498845037755</v>
       </c>
       <c r="T50">
-        <v>1.362696663043668</v>
+        <v>1.384546756138101</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.584515952760007</v>
+        <v>6.450138076173069</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0905093410969255</v>
+        <v>0.09026077366047676</v>
       </c>
       <c r="C51">
-        <v>755.3546404120166</v>
+        <v>750.538837164245</v>
       </c>
       <c r="D51">
-        <v>1269.640640412017</v>
+        <v>1276.738837164245</v>
       </c>
       <c r="E51">
-        <v>-100.414</v>
+        <v>-88.5</v>
       </c>
       <c r="F51">
-        <v>583.7860000000001</v>
+        <v>595.7</v>
       </c>
       <c r="G51">
         <v>69.5</v>
@@ -5475,28 +5475,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M51">
-        <v>31.6995798</v>
+        <v>32.34651</v>
       </c>
       <c r="N51">
-        <v>172.7670868666667</v>
+        <v>172.1201566666667</v>
       </c>
       <c r="O51">
-        <v>51.83012606</v>
+        <v>51.63604700000001</v>
       </c>
       <c r="P51">
-        <v>120.9369608066667</v>
+        <v>120.4841096666667</v>
       </c>
       <c r="Q51">
-        <v>205.1369608066667</v>
+        <v>204.6841096666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1409498845037755</v>
+        <v>0.1425115473209535</v>
       </c>
       <c r="T51">
-        <v>1.384546756138101</v>
+        <v>1.407270852956311</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.450138076173069</v>
+        <v>6.321135314649608</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09026077366047676</v>
+        <v>0.09001220622402803</v>
       </c>
       <c r="C52">
-        <v>750.538837164245</v>
+        <v>745.8028480999665</v>
       </c>
       <c r="D52">
-        <v>1276.738837164245</v>
+        <v>1283.916848099967</v>
       </c>
       <c r="E52">
-        <v>-88.5</v>
+        <v>-76.58600000000001</v>
       </c>
       <c r="F52">
-        <v>595.7</v>
+        <v>607.614</v>
       </c>
       <c r="G52">
         <v>69.5</v>
@@ -5557,28 +5557,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M52">
-        <v>32.34651</v>
+        <v>32.9934402</v>
       </c>
       <c r="N52">
-        <v>172.1201566666667</v>
+        <v>171.4732264666667</v>
       </c>
       <c r="O52">
-        <v>51.63604700000001</v>
+        <v>51.44196794</v>
       </c>
       <c r="P52">
-        <v>120.4841096666667</v>
+        <v>120.0312585266667</v>
       </c>
       <c r="Q52">
-        <v>204.6841096666667</v>
+        <v>204.2312585266667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1425115473209535</v>
+        <v>0.1441369514776082</v>
       </c>
       <c r="T52">
-        <v>1.407270852956311</v>
+        <v>1.430922463930367</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.321135314649608</v>
+        <v>6.197191484950595</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09001220622402803</v>
+        <v>0.09012763878757928</v>
       </c>
       <c r="C53">
-        <v>745.8028480999665</v>
+        <v>730.5454303764775</v>
       </c>
       <c r="D53">
-        <v>1283.916848099967</v>
+        <v>1280.573430376478</v>
       </c>
       <c r="E53">
-        <v>-76.58600000000001</v>
+        <v>-64.67200000000003</v>
       </c>
       <c r="F53">
-        <v>607.614</v>
+        <v>619.528</v>
       </c>
       <c r="G53">
         <v>69.5</v>
@@ -5639,45 +5639,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M53">
-        <v>32.9934402</v>
+        <v>34.2598984</v>
       </c>
       <c r="N53">
-        <v>171.4732264666667</v>
+        <v>170.2067682666667</v>
       </c>
       <c r="O53">
-        <v>51.44196794</v>
+        <v>51.06203048000001</v>
       </c>
       <c r="P53">
-        <v>120.0312585266667</v>
+        <v>119.1447377866667</v>
       </c>
       <c r="Q53">
-        <v>204.2312585266667</v>
+        <v>203.3447377866667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1441369514776082</v>
+        <v>0.1458300808074568</v>
       </c>
       <c r="T53">
-        <v>1.430922463930367</v>
+        <v>1.455559558695008</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.197191484950595</v>
+        <v>5.968104875251663</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09012763878757928</v>
+        <v>0.08988607135113054</v>
       </c>
       <c r="C54">
-        <v>730.5454303764775</v>
+        <v>725.6482688308857</v>
       </c>
       <c r="D54">
-        <v>1280.573430376478</v>
+        <v>1287.590268830886</v>
       </c>
       <c r="E54">
-        <v>-64.67200000000003</v>
+        <v>-52.75799999999992</v>
       </c>
       <c r="F54">
-        <v>619.528</v>
+        <v>631.4420000000001</v>
       </c>
       <c r="G54">
         <v>69.5</v>
@@ -5721,28 +5721,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M54">
-        <v>34.2598984</v>
+        <v>34.91874260000001</v>
       </c>
       <c r="N54">
-        <v>170.2067682666667</v>
+        <v>169.5479240666667</v>
       </c>
       <c r="O54">
-        <v>51.06203048000001</v>
+        <v>50.86437722000001</v>
       </c>
       <c r="P54">
-        <v>119.1447377866667</v>
+        <v>118.6835468466667</v>
       </c>
       <c r="Q54">
-        <v>203.3447377866667</v>
+        <v>202.8835468466667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1458300808074568</v>
+        <v>0.1475952581938948</v>
       </c>
       <c r="T54">
-        <v>1.455559558695008</v>
+        <v>1.481245040470911</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.968104875251663</v>
+        <v>5.855499122888424</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08988607135113054</v>
+        <v>0.08964450391468179</v>
       </c>
       <c r="C55">
-        <v>725.6482688308857</v>
+        <v>720.8284277941874</v>
       </c>
       <c r="D55">
-        <v>1287.590268830886</v>
+        <v>1294.684427794188</v>
       </c>
       <c r="E55">
-        <v>-52.75799999999992</v>
+        <v>-40.84399999999994</v>
       </c>
       <c r="F55">
-        <v>631.4420000000001</v>
+        <v>643.3560000000001</v>
       </c>
       <c r="G55">
         <v>69.5</v>
@@ -5803,28 +5803,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M55">
-        <v>34.91874260000001</v>
+        <v>35.57758680000001</v>
       </c>
       <c r="N55">
-        <v>169.5479240666667</v>
+        <v>168.8890798666667</v>
       </c>
       <c r="O55">
-        <v>50.86437722000001</v>
+        <v>50.66672396000001</v>
       </c>
       <c r="P55">
-        <v>118.6835468466667</v>
+        <v>118.2223559066667</v>
       </c>
       <c r="Q55">
-        <v>202.8835468466667</v>
+        <v>202.4223559066667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1475952581938948</v>
+        <v>0.1494371824232213</v>
       </c>
       <c r="T55">
-        <v>1.481245040470911</v>
+        <v>1.508047282324027</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.855499122888424</v>
+        <v>5.747063953946046</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08964450391468179</v>
+        <v>0.08940293647823305</v>
       </c>
       <c r="C56">
-        <v>720.8284277941874</v>
+        <v>716.0871923713727</v>
       </c>
       <c r="D56">
-        <v>1294.684427794188</v>
+        <v>1301.857192371373</v>
       </c>
       <c r="E56">
-        <v>-40.84399999999994</v>
+        <v>-28.92999999999995</v>
       </c>
       <c r="F56">
-        <v>643.3560000000001</v>
+        <v>655.2700000000001</v>
       </c>
       <c r="G56">
         <v>69.5</v>
@@ -5885,28 +5885,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M56">
-        <v>35.57758680000001</v>
+        <v>36.236431</v>
       </c>
       <c r="N56">
-        <v>168.8890798666667</v>
+        <v>168.2302356666667</v>
       </c>
       <c r="O56">
-        <v>50.66672396000001</v>
+        <v>50.4690707</v>
       </c>
       <c r="P56">
-        <v>118.2223559066667</v>
+        <v>117.7611649666667</v>
       </c>
       <c r="Q56">
-        <v>202.4223559066667</v>
+        <v>201.9611649666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1494371824232213</v>
+        <v>0.151360969951629</v>
       </c>
       <c r="T56">
-        <v>1.508047282324027</v>
+        <v>1.53604073492617</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.747063953946046</v>
+        <v>5.642571882056118</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08940293647823305</v>
+        <v>0.0891613690417843</v>
       </c>
       <c r="C57">
-        <v>716.0871923713727</v>
+        <v>711.4258763048637</v>
       </c>
       <c r="D57">
-        <v>1301.857192371373</v>
+        <v>1309.109876304864</v>
       </c>
       <c r="E57">
-        <v>-28.92999999999995</v>
+        <v>-17.01599999999996</v>
       </c>
       <c r="F57">
-        <v>655.2700000000001</v>
+        <v>667.1840000000001</v>
       </c>
       <c r="G57">
         <v>69.5</v>
@@ -5967,28 +5967,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M57">
-        <v>36.236431</v>
+        <v>36.89527520000001</v>
       </c>
       <c r="N57">
-        <v>168.2302356666667</v>
+        <v>167.5713914666667</v>
       </c>
       <c r="O57">
-        <v>50.4690707</v>
+        <v>50.27141744</v>
       </c>
       <c r="P57">
-        <v>117.7611649666667</v>
+        <v>117.2999740266667</v>
       </c>
       <c r="Q57">
-        <v>201.9611649666667</v>
+        <v>201.4999740266667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.151360969951629</v>
+        <v>0.1533722023676916</v>
       </c>
       <c r="T57">
-        <v>1.53604073492617</v>
+        <v>1.565306617192047</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.642571882056118</v>
+        <v>5.541811669876544</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0891613690417843</v>
+        <v>0.08891980160533557</v>
       </c>
       <c r="C58">
-        <v>711.4258763048637</v>
+        <v>706.8458227766756</v>
       </c>
       <c r="D58">
-        <v>1309.109876304864</v>
+        <v>1316.443822776676</v>
       </c>
       <c r="E58">
-        <v>-17.01599999999996</v>
+        <v>-5.101999999999975</v>
       </c>
       <c r="F58">
-        <v>667.1840000000001</v>
+        <v>679.0980000000001</v>
       </c>
       <c r="G58">
         <v>69.5</v>
@@ -6049,28 +6049,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M58">
-        <v>36.89527520000001</v>
+        <v>37.5541194</v>
       </c>
       <c r="N58">
-        <v>167.5713914666667</v>
+        <v>166.9125472666667</v>
       </c>
       <c r="O58">
-        <v>50.27141744</v>
+        <v>50.07376418000001</v>
       </c>
       <c r="P58">
-        <v>117.2999740266667</v>
+        <v>116.8387830866667</v>
       </c>
       <c r="Q58">
-        <v>201.4999740266667</v>
+        <v>201.0387830866667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1533722023676916</v>
+        <v>0.1554769804775246</v>
       </c>
       <c r="T58">
-        <v>1.565306617192047</v>
+        <v>1.595933703284244</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.541811669876544</v>
+        <v>5.44458690373836</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08891980160533557</v>
+        <v>0.08867823416888683</v>
       </c>
       <c r="C59">
-        <v>706.8458227766756</v>
+        <v>702.3484052377066</v>
       </c>
       <c r="D59">
-        <v>1316.443822776676</v>
+        <v>1323.860405237707</v>
       </c>
       <c r="E59">
-        <v>-5.101999999999975</v>
+        <v>6.812000000000126</v>
       </c>
       <c r="F59">
-        <v>679.0980000000001</v>
+        <v>691.0120000000002</v>
       </c>
       <c r="G59">
         <v>69.5</v>
@@ -6131,28 +6131,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M59">
-        <v>37.5541194</v>
+        <v>38.21296360000001</v>
       </c>
       <c r="N59">
-        <v>166.9125472666667</v>
+        <v>166.2537030666667</v>
       </c>
       <c r="O59">
-        <v>50.07376418000001</v>
+        <v>49.87611092</v>
       </c>
       <c r="P59">
-        <v>116.8387830866667</v>
+        <v>116.3775921466667</v>
       </c>
       <c r="Q59">
-        <v>201.0387830866667</v>
+        <v>200.5775921466667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1554769804775246</v>
+        <v>0.1576819861163972</v>
       </c>
       <c r="T59">
-        <v>1.595933703284244</v>
+        <v>1.628019222047497</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.44458690373836</v>
+        <v>5.35071471574287</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08867823416888682</v>
+        <v>0.08843666673243808</v>
       </c>
       <c r="C60">
-        <v>702.348405237707</v>
+        <v>697.9350282652091</v>
       </c>
       <c r="D60">
-        <v>1323.860405237707</v>
+        <v>1331.361028265209</v>
       </c>
       <c r="E60">
-        <v>6.812000000000012</v>
+        <v>18.726</v>
       </c>
       <c r="F60">
-        <v>691.0120000000001</v>
+        <v>702.926</v>
       </c>
       <c r="G60">
         <v>69.5</v>
@@ -6213,28 +6213,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M60">
-        <v>38.2129636</v>
+        <v>38.87180780000001</v>
       </c>
       <c r="N60">
-        <v>166.2537030666667</v>
+        <v>165.5948588666667</v>
       </c>
       <c r="O60">
-        <v>49.87611092000001</v>
+        <v>49.67845766000001</v>
       </c>
       <c r="P60">
-        <v>116.3775921466667</v>
+        <v>115.9164012066667</v>
       </c>
       <c r="Q60">
-        <v>200.5775921466667</v>
+        <v>200.1164012066667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1576819861163972</v>
+        <v>0.1599945530059465</v>
       </c>
       <c r="T60">
-        <v>1.628019222047497</v>
+        <v>1.661669888067495</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.350714715742871</v>
+        <v>5.260024635815026</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08843666673243808</v>
+        <v>0.08819509929598934</v>
       </c>
       <c r="C61">
-        <v>697.9350282652091</v>
+        <v>693.6071284495812</v>
       </c>
       <c r="D61">
-        <v>1331.361028265209</v>
+        <v>1338.947128449581</v>
       </c>
       <c r="E61">
-        <v>18.726</v>
+        <v>30.63999999999999</v>
       </c>
       <c r="F61">
-        <v>702.926</v>
+        <v>714.84</v>
       </c>
       <c r="G61">
         <v>69.5</v>
@@ -6295,28 +6295,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M61">
-        <v>38.87180780000001</v>
+        <v>39.530652</v>
       </c>
       <c r="N61">
-        <v>165.5948588666667</v>
+        <v>164.9360146666667</v>
       </c>
       <c r="O61">
-        <v>49.67845766000001</v>
+        <v>49.4808044</v>
       </c>
       <c r="P61">
-        <v>115.9164012066667</v>
+        <v>115.4552102666667</v>
       </c>
       <c r="Q61">
-        <v>200.1164012066667</v>
+        <v>199.6552102666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1599945530059465</v>
+        <v>0.1624227482399734</v>
       </c>
       <c r="T61">
-        <v>1.661669888067495</v>
+        <v>1.697003087388493</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.260024635815026</v>
+        <v>5.172357558551442</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08819509929598934</v>
+        <v>0.08795353185954059</v>
       </c>
       <c r="C62">
-        <v>693.6071284495812</v>
+        <v>689.3661753116504</v>
       </c>
       <c r="D62">
-        <v>1338.947128449581</v>
+        <v>1346.62017531165</v>
       </c>
       <c r="E62">
-        <v>30.63999999999999</v>
+        <v>42.55399999999997</v>
       </c>
       <c r="F62">
-        <v>714.84</v>
+        <v>726.754</v>
       </c>
       <c r="G62">
         <v>69.5</v>
@@ -6377,28 +6377,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M62">
-        <v>39.530652</v>
+        <v>40.1894962</v>
       </c>
       <c r="N62">
-        <v>164.9360146666667</v>
+        <v>164.2771704666667</v>
       </c>
       <c r="O62">
-        <v>49.4808044</v>
+        <v>49.28315114000001</v>
       </c>
       <c r="P62">
-        <v>115.4552102666667</v>
+        <v>114.9940193266667</v>
       </c>
       <c r="Q62">
-        <v>199.6552102666667</v>
+        <v>199.1940193266667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1624227482399734</v>
+        <v>0.1649754663065144</v>
       </c>
       <c r="T62">
-        <v>1.697003087388493</v>
+        <v>1.734148245649029</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.172357558551442</v>
+        <v>5.087564811689943</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08795353185954059</v>
+        <v>0.08771196442309186</v>
       </c>
       <c r="C63">
-        <v>689.3661753116504</v>
+        <v>685.2136722516735</v>
       </c>
       <c r="D63">
-        <v>1346.62017531165</v>
+        <v>1354.381672251674</v>
       </c>
       <c r="E63">
-        <v>42.55399999999997</v>
+        <v>54.46799999999996</v>
       </c>
       <c r="F63">
-        <v>726.754</v>
+        <v>738.668</v>
       </c>
       <c r="G63">
         <v>69.5</v>
@@ -6459,28 +6459,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M63">
-        <v>40.1894962</v>
+        <v>40.8483404</v>
       </c>
       <c r="N63">
-        <v>164.2771704666667</v>
+        <v>163.6183262666667</v>
       </c>
       <c r="O63">
-        <v>49.28315114000001</v>
+        <v>49.08549788000001</v>
       </c>
       <c r="P63">
-        <v>114.9940193266667</v>
+        <v>114.5328283866667</v>
       </c>
       <c r="Q63">
-        <v>199.1940193266667</v>
+        <v>198.7328283866667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1649754663065144</v>
+        <v>0.1676625379555049</v>
       </c>
       <c r="T63">
-        <v>1.734148245649029</v>
+        <v>1.773248412239067</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.087564811689943</v>
+        <v>5.005507314727201</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08771196442309186</v>
+        <v>0.08747039698664312</v>
       </c>
       <c r="C64">
-        <v>685.2136722516735</v>
+        <v>681.1511575313521</v>
       </c>
       <c r="D64">
-        <v>1354.381672251674</v>
+        <v>1362.233157531352</v>
       </c>
       <c r="E64">
-        <v>54.46799999999996</v>
+        <v>66.38200000000006</v>
       </c>
       <c r="F64">
-        <v>738.668</v>
+        <v>750.5820000000001</v>
       </c>
       <c r="G64">
         <v>69.5</v>
@@ -6541,28 +6541,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M64">
-        <v>40.8483404</v>
+        <v>41.50718460000001</v>
       </c>
       <c r="N64">
-        <v>163.6183262666667</v>
+        <v>162.9594820666667</v>
       </c>
       <c r="O64">
-        <v>49.08549788000001</v>
+        <v>48.88784462</v>
       </c>
       <c r="P64">
-        <v>114.5328283866667</v>
+        <v>114.0716374466667</v>
       </c>
       <c r="Q64">
-        <v>198.7328283866667</v>
+        <v>198.2716374466667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1676625379555049</v>
+        <v>0.1704948567206571</v>
       </c>
       <c r="T64">
-        <v>1.773248412239067</v>
+        <v>1.814462101347486</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.005507314727201</v>
+        <v>4.926054817668039</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08747039698664312</v>
+        <v>0.08722882955019437</v>
       </c>
       <c r="C65">
-        <v>681.1511575313521</v>
+        <v>677.1802052901992</v>
       </c>
       <c r="D65">
-        <v>1362.233157531352</v>
+        <v>1370.176205290199</v>
       </c>
       <c r="E65">
-        <v>66.38200000000006</v>
+        <v>78.29600000000005</v>
       </c>
       <c r="F65">
-        <v>750.5820000000001</v>
+        <v>762.4960000000001</v>
       </c>
       <c r="G65">
         <v>69.5</v>
@@ -6623,28 +6623,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M65">
-        <v>41.50718460000001</v>
+        <v>42.16602880000001</v>
       </c>
       <c r="N65">
-        <v>162.9594820666667</v>
+        <v>162.3006378666667</v>
       </c>
       <c r="O65">
-        <v>48.88784462</v>
+        <v>48.69019136000001</v>
       </c>
       <c r="P65">
-        <v>114.0716374466667</v>
+        <v>113.6104465066667</v>
       </c>
       <c r="Q65">
-        <v>198.2716374466667</v>
+        <v>197.8104465066667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1704948567206571</v>
+        <v>0.1734845265283177</v>
       </c>
       <c r="T65">
-        <v>1.814462101347486</v>
+        <v>1.857965439850816</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.926054817668039</v>
+        <v>4.849085211141977</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08722882955019437</v>
+        <v>0.08698726211374563</v>
       </c>
       <c r="C66">
-        <v>677.1802052901992</v>
+        <v>673.3024265976735</v>
       </c>
       <c r="D66">
-        <v>1370.176205290199</v>
+        <v>1378.212426597674</v>
       </c>
       <c r="E66">
-        <v>78.29600000000005</v>
+        <v>90.21000000000004</v>
       </c>
       <c r="F66">
-        <v>762.4960000000001</v>
+        <v>774.4100000000001</v>
       </c>
       <c r="G66">
         <v>69.5</v>
@@ -6705,28 +6705,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M66">
-        <v>42.16602880000001</v>
+        <v>42.824873</v>
       </c>
       <c r="N66">
-        <v>162.3006378666667</v>
+        <v>161.6417936666667</v>
       </c>
       <c r="O66">
-        <v>48.69019136000001</v>
+        <v>48.49253810000001</v>
       </c>
       <c r="P66">
-        <v>113.6104465066667</v>
+        <v>113.1492555666667</v>
       </c>
       <c r="Q66">
-        <v>197.8104465066667</v>
+        <v>197.3492555666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1734845265283177</v>
+        <v>0.1766450346107018</v>
       </c>
       <c r="T66">
-        <v>1.857965439850816</v>
+        <v>1.90395468341148</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.849085211141977</v>
+        <v>4.774483900201331</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08698726211374563</v>
+        <v>0.0867456946772969</v>
       </c>
       <c r="C67">
-        <v>673.3024265976735</v>
+        <v>669.5194705425597</v>
       </c>
       <c r="D67">
-        <v>1378.212426597674</v>
+        <v>1386.34347054256</v>
       </c>
       <c r="E67">
-        <v>90.21000000000004</v>
+        <v>102.124</v>
       </c>
       <c r="F67">
-        <v>774.4100000000001</v>
+        <v>786.3240000000001</v>
       </c>
       <c r="G67">
         <v>69.5</v>
@@ -6787,28 +6787,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M67">
-        <v>42.824873</v>
+        <v>43.48371720000001</v>
       </c>
       <c r="N67">
-        <v>161.6417936666667</v>
+        <v>160.9829494666667</v>
       </c>
       <c r="O67">
-        <v>48.49253810000001</v>
+        <v>48.29488484000001</v>
       </c>
       <c r="P67">
-        <v>113.1492555666667</v>
+        <v>112.6880646266667</v>
       </c>
       <c r="Q67">
-        <v>197.3492555666667</v>
+        <v>196.8880646266667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1766450346107018</v>
+        <v>0.1799914549332262</v>
       </c>
       <c r="T67">
-        <v>1.90395468341148</v>
+        <v>1.952649176593359</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.774483900201331</v>
+        <v>4.702143235046766</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0867456946772969</v>
+        <v>0.08650412724084816</v>
       </c>
       <c r="C68">
-        <v>669.5194705425597</v>
+        <v>665.8330253611368</v>
       </c>
       <c r="D68">
-        <v>1386.34347054256</v>
+        <v>1394.571025361137</v>
       </c>
       <c r="E68">
-        <v>102.124</v>
+        <v>114.038</v>
       </c>
       <c r="F68">
-        <v>786.3240000000001</v>
+        <v>798.2380000000001</v>
       </c>
       <c r="G68">
         <v>69.5</v>
@@ -6869,28 +6869,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M68">
-        <v>43.48371720000001</v>
+        <v>44.14256140000001</v>
       </c>
       <c r="N68">
-        <v>160.9829494666667</v>
+        <v>160.3241052666667</v>
       </c>
       <c r="O68">
-        <v>48.29488484000001</v>
+        <v>48.09723158000001</v>
       </c>
       <c r="P68">
-        <v>112.6880646266667</v>
+        <v>112.2268736866667</v>
       </c>
       <c r="Q68">
-        <v>196.8880646266667</v>
+        <v>196.4268736866667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1799914549332262</v>
+        <v>0.1835406886086308</v>
       </c>
       <c r="T68">
-        <v>1.952649176593359</v>
+        <v>2.004294851180201</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.702143235046766</v>
+        <v>4.631961992732634</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08650412724084816</v>
+        <v>0.08626255980439942</v>
       </c>
       <c r="C69">
-        <v>665.8330253611368</v>
+        <v>662.2448196057595</v>
       </c>
       <c r="D69">
-        <v>1394.571025361137</v>
+        <v>1402.89681960576</v>
       </c>
       <c r="E69">
-        <v>114.038</v>
+        <v>125.9520000000001</v>
       </c>
       <c r="F69">
-        <v>798.2380000000001</v>
+        <v>810.1520000000002</v>
       </c>
       <c r="G69">
         <v>69.5</v>
@@ -6951,28 +6951,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M69">
-        <v>44.14256140000001</v>
+        <v>44.80140560000001</v>
       </c>
       <c r="N69">
-        <v>160.3241052666667</v>
+        <v>159.6652610666667</v>
       </c>
       <c r="O69">
-        <v>48.09723158000001</v>
+        <v>47.89957832</v>
       </c>
       <c r="P69">
-        <v>112.2268736866667</v>
+        <v>111.7656827466667</v>
       </c>
       <c r="Q69">
-        <v>196.4268736866667</v>
+        <v>195.9656827466667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1835406886086308</v>
+        <v>0.1873117493887482</v>
       </c>
       <c r="T69">
-        <v>2.004294851180201</v>
+        <v>2.05916838042872</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.631961992732634</v>
+        <v>4.563844904604213</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08626255980439942</v>
+        <v>0.08722849236795067</v>
       </c>
       <c r="C70">
-        <v>662.2448196057595</v>
+        <v>617.6213570135845</v>
       </c>
       <c r="D70">
-        <v>1402.89681960576</v>
+        <v>1370.187357013585</v>
       </c>
       <c r="E70">
-        <v>125.9520000000001</v>
+        <v>137.8660000000001</v>
       </c>
       <c r="F70">
-        <v>810.1520000000002</v>
+        <v>822.0660000000001</v>
       </c>
       <c r="G70">
         <v>69.5</v>
@@ -7033,45 +7033,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M70">
-        <v>44.80140560000001</v>
+        <v>47.51541480000001</v>
       </c>
       <c r="N70">
-        <v>159.6652610666667</v>
+        <v>156.9512518666667</v>
       </c>
       <c r="O70">
-        <v>47.89957832</v>
+        <v>47.08537556000001</v>
       </c>
       <c r="P70">
-        <v>111.7656827466667</v>
+        <v>109.8658763066667</v>
       </c>
       <c r="Q70">
-        <v>195.9656827466667</v>
+        <v>194.0658763066667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1873117493887482</v>
+        <v>0.1913261044127441</v>
       </c>
       <c r="T70">
-        <v>2.05916838042872</v>
+        <v>2.117582137370693</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.563844904604213</v>
+        <v>4.30316493136595</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08722849236795067</v>
+        <v>0.08700442493150193</v>
       </c>
       <c r="C71">
-        <v>617.6213570135845</v>
+        <v>613.1583618280164</v>
       </c>
       <c r="D71">
-        <v>1370.187357013585</v>
+        <v>1377.638361828017</v>
       </c>
       <c r="E71">
-        <v>137.8660000000001</v>
+        <v>149.7800000000001</v>
       </c>
       <c r="F71">
-        <v>822.0660000000001</v>
+        <v>833.9800000000001</v>
       </c>
       <c r="G71">
         <v>69.5</v>
@@ -7115,28 +7115,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M71">
-        <v>47.51541480000001</v>
+        <v>48.20404400000001</v>
       </c>
       <c r="N71">
-        <v>156.9512518666667</v>
+        <v>156.2626226666667</v>
       </c>
       <c r="O71">
-        <v>47.08537556000001</v>
+        <v>46.87878680000001</v>
       </c>
       <c r="P71">
-        <v>109.8658763066667</v>
+        <v>109.3838358666667</v>
       </c>
       <c r="Q71">
-        <v>194.0658763066667</v>
+        <v>193.5838358666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1913261044127441</v>
+        <v>0.1956080831050065</v>
       </c>
       <c r="T71">
-        <v>2.117582137370693</v>
+        <v>2.179890144775463</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.30316493136595</v>
+        <v>4.241691146632151</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08700442493150193</v>
+        <v>0.0867803574950532</v>
       </c>
       <c r="C72">
-        <v>613.1583618280164</v>
+        <v>608.7768460462299</v>
       </c>
       <c r="D72">
-        <v>1377.638361828017</v>
+        <v>1385.17084604623</v>
       </c>
       <c r="E72">
-        <v>149.7800000000001</v>
+        <v>161.6940000000001</v>
       </c>
       <c r="F72">
-        <v>833.9800000000001</v>
+        <v>845.8940000000001</v>
       </c>
       <c r="G72">
         <v>69.5</v>
@@ -7197,28 +7197,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M72">
-        <v>48.20404400000001</v>
+        <v>48.89267320000001</v>
       </c>
       <c r="N72">
-        <v>156.2626226666667</v>
+        <v>155.5739934666667</v>
       </c>
       <c r="O72">
-        <v>46.87878680000001</v>
+        <v>46.67219804</v>
       </c>
       <c r="P72">
-        <v>109.3838358666667</v>
+        <v>108.9017954266667</v>
       </c>
       <c r="Q72">
-        <v>193.5838358666667</v>
+        <v>193.1017954266667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1956080831050065</v>
+        <v>0.2001853706725972</v>
       </c>
       <c r="T72">
-        <v>2.179890144775463</v>
+        <v>2.246495256139183</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.241691146632151</v>
+        <v>4.181949017806346</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0867803574950532</v>
+        <v>0.08655629005860446</v>
       </c>
       <c r="C73">
-        <v>608.77684604623</v>
+        <v>604.4781535256598</v>
       </c>
       <c r="D73">
-        <v>1385.17084604623</v>
+        <v>1392.78615352566</v>
       </c>
       <c r="E73">
-        <v>161.694</v>
+        <v>173.6079999999999</v>
       </c>
       <c r="F73">
-        <v>845.894</v>
+        <v>857.808</v>
       </c>
       <c r="G73">
         <v>69.5</v>
@@ -7279,28 +7279,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M73">
-        <v>48.8926732</v>
+        <v>49.58130240000001</v>
       </c>
       <c r="N73">
-        <v>155.5739934666667</v>
+        <v>154.8853642666667</v>
       </c>
       <c r="O73">
-        <v>46.67219804000001</v>
+        <v>46.46560928000001</v>
       </c>
       <c r="P73">
-        <v>108.9017954266667</v>
+        <v>108.4197549866667</v>
       </c>
       <c r="Q73">
-        <v>193.1017954266667</v>
+        <v>192.6197549866667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2001853706725972</v>
+        <v>0.2050896073521588</v>
       </c>
       <c r="T73">
-        <v>2.246495256139182</v>
+        <v>2.317857875457454</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.181949017806346</v>
+        <v>4.123866392559036</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08655629005860446</v>
+        <v>0.08633222262215572</v>
       </c>
       <c r="C74">
-        <v>604.4781535256598</v>
+        <v>600.2636578398204</v>
       </c>
       <c r="D74">
-        <v>1392.78615352566</v>
+        <v>1400.485657839821</v>
       </c>
       <c r="E74">
-        <v>173.6079999999999</v>
+        <v>185.522</v>
       </c>
       <c r="F74">
-        <v>857.808</v>
+        <v>869.7220000000001</v>
       </c>
       <c r="G74">
         <v>69.5</v>
@@ -7361,28 +7361,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M74">
-        <v>49.58130240000001</v>
+        <v>50.26993160000001</v>
       </c>
       <c r="N74">
-        <v>154.8853642666667</v>
+        <v>154.1967350666667</v>
       </c>
       <c r="O74">
-        <v>46.46560928000001</v>
+        <v>46.25902052000001</v>
       </c>
       <c r="P74">
-        <v>108.4197549866667</v>
+        <v>107.9377145466667</v>
       </c>
       <c r="Q74">
-        <v>192.6197549866667</v>
+        <v>192.1377145466667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2050896073521588</v>
+        <v>0.2103571208227989</v>
       </c>
       <c r="T74">
-        <v>2.317857875457454</v>
+        <v>2.394506614725227</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.123866392559036</v>
+        <v>4.067375072113022</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08633222262215572</v>
+        <v>0.08610815518570697</v>
       </c>
       <c r="C75">
-        <v>600.2636578398204</v>
+        <v>596.1347631042428</v>
       </c>
       <c r="D75">
-        <v>1400.485657839821</v>
+        <v>1408.270763104243</v>
       </c>
       <c r="E75">
-        <v>185.522</v>
+        <v>197.436</v>
       </c>
       <c r="F75">
-        <v>869.7220000000001</v>
+        <v>881.6360000000001</v>
       </c>
       <c r="G75">
         <v>69.5</v>
@@ -7443,28 +7443,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M75">
-        <v>50.26993160000001</v>
+        <v>50.95856080000001</v>
       </c>
       <c r="N75">
-        <v>154.1967350666667</v>
+        <v>153.5081058666667</v>
       </c>
       <c r="O75">
-        <v>46.25902052000001</v>
+        <v>46.05243176</v>
       </c>
       <c r="P75">
-        <v>107.9377145466667</v>
+        <v>107.4556741066667</v>
       </c>
       <c r="Q75">
-        <v>192.1377145466667</v>
+        <v>191.6556741066667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2103571208227989</v>
+        <v>0.2160298276373345</v>
       </c>
       <c r="T75">
-        <v>2.394506614725227</v>
+        <v>2.477051410859751</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.067375072113022</v>
+        <v>4.012410544111495</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08610815518570697</v>
+        <v>0.08772158774925821</v>
       </c>
       <c r="C76">
-        <v>596.1347631042428</v>
+        <v>530.0207666470534</v>
       </c>
       <c r="D76">
-        <v>1408.270763104243</v>
+        <v>1354.070766647053</v>
       </c>
       <c r="E76">
-        <v>197.436</v>
+        <v>209.35</v>
       </c>
       <c r="F76">
-        <v>881.6360000000001</v>
+        <v>893.5500000000001</v>
       </c>
       <c r="G76">
         <v>69.5</v>
@@ -7525,45 +7525,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M76">
-        <v>50.95856080000001</v>
+        <v>54.774615</v>
       </c>
       <c r="N76">
-        <v>153.5081058666667</v>
+        <v>149.6920516666667</v>
       </c>
       <c r="O76">
-        <v>46.05243176</v>
+        <v>44.90761550000001</v>
       </c>
       <c r="P76">
-        <v>107.4556741066667</v>
+        <v>104.7844361666667</v>
       </c>
       <c r="Q76">
-        <v>191.6556741066667</v>
+        <v>188.9844361666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2160298276373345</v>
+        <v>0.2221563509970329</v>
       </c>
       <c r="T76">
-        <v>2.477051410859751</v>
+        <v>2.566199790685038</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.3</v>
       </c>
       <c r="W76">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.012410544111495</v>
+        <v>3.732872730673993</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08772158774925821</v>
+        <v>0.08752202031280948</v>
       </c>
       <c r="C77">
-        <v>530.0207666470534</v>
+        <v>524.583644555743</v>
       </c>
       <c r="D77">
-        <v>1354.070766647053</v>
+        <v>1360.547644555743</v>
       </c>
       <c r="E77">
-        <v>209.35</v>
+        <v>221.264</v>
       </c>
       <c r="F77">
-        <v>893.5500000000001</v>
+        <v>905.4640000000001</v>
       </c>
       <c r="G77">
         <v>69.5</v>
@@ -7607,28 +7607,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M77">
-        <v>54.774615</v>
+        <v>55.50494320000001</v>
       </c>
       <c r="N77">
-        <v>149.6920516666667</v>
+        <v>148.9617234666667</v>
       </c>
       <c r="O77">
-        <v>44.90761550000001</v>
+        <v>44.68851704</v>
       </c>
       <c r="P77">
-        <v>104.7844361666667</v>
+        <v>104.2732064266667</v>
       </c>
       <c r="Q77">
-        <v>188.9844361666667</v>
+        <v>188.4732064266667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2221563509970329</v>
+        <v>0.2287934179700395</v>
       </c>
       <c r="T77">
-        <v>2.566199790685038</v>
+        <v>2.662777202162432</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.732872730673993</v>
+        <v>3.683755984217756</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08752202031280948</v>
+        <v>0.08732245287636073</v>
       </c>
       <c r="C78">
-        <v>524.583644555743</v>
+        <v>519.2087814992868</v>
       </c>
       <c r="D78">
-        <v>1360.547644555743</v>
+        <v>1367.086781499287</v>
       </c>
       <c r="E78">
-        <v>221.264</v>
+        <v>233.178</v>
       </c>
       <c r="F78">
-        <v>905.4640000000001</v>
+        <v>917.378</v>
       </c>
       <c r="G78">
         <v>69.5</v>
@@ -7689,28 +7689,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M78">
-        <v>55.50494320000001</v>
+        <v>56.2352714</v>
       </c>
       <c r="N78">
-        <v>148.9617234666667</v>
+        <v>148.2313952666667</v>
       </c>
       <c r="O78">
-        <v>44.68851704</v>
+        <v>44.46941858000001</v>
       </c>
       <c r="P78">
-        <v>104.2732064266667</v>
+        <v>103.7619766866667</v>
       </c>
       <c r="Q78">
-        <v>188.4732064266667</v>
+        <v>187.9619766866667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2287934179700395</v>
+        <v>0.2360076212015684</v>
       </c>
       <c r="T78">
-        <v>2.662777202162432</v>
+        <v>2.767752649420469</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.683755984217756</v>
+        <v>3.635914997409734</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08732245287636073</v>
+        <v>0.08712288543991199</v>
       </c>
       <c r="C79">
-        <v>519.2087814992868</v>
+        <v>513.8970795112077</v>
       </c>
       <c r="D79">
-        <v>1367.086781499287</v>
+        <v>1373.689079511208</v>
       </c>
       <c r="E79">
-        <v>233.178</v>
+        <v>245.0920000000001</v>
       </c>
       <c r="F79">
-        <v>917.378</v>
+        <v>929.2920000000001</v>
       </c>
       <c r="G79">
         <v>69.5</v>
@@ -7771,28 +7771,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M79">
-        <v>56.2352714</v>
+        <v>56.96559960000001</v>
       </c>
       <c r="N79">
-        <v>148.2313952666667</v>
+        <v>147.5010670666667</v>
       </c>
       <c r="O79">
-        <v>44.46941858000001</v>
+        <v>44.25032012</v>
       </c>
       <c r="P79">
-        <v>103.7619766866667</v>
+        <v>103.2507469466667</v>
       </c>
       <c r="Q79">
-        <v>187.9619766866667</v>
+        <v>187.4507469466667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2360076212015684</v>
+        <v>0.2438776610905091</v>
       </c>
       <c r="T79">
-        <v>2.767752649420469</v>
+        <v>2.882271319156509</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.635914997409734</v>
+        <v>3.589300702571147</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08712288543991199</v>
+        <v>0.08692331800346326</v>
       </c>
       <c r="C80">
-        <v>513.8970795112077</v>
+        <v>508.6494581349507</v>
       </c>
       <c r="D80">
-        <v>1373.689079511208</v>
+        <v>1380.355458134951</v>
       </c>
       <c r="E80">
-        <v>245.0920000000001</v>
+        <v>257.0060000000001</v>
       </c>
       <c r="F80">
-        <v>929.2920000000001</v>
+        <v>941.2060000000001</v>
       </c>
       <c r="G80">
         <v>69.5</v>
@@ -7853,28 +7853,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M80">
-        <v>56.96559960000001</v>
+        <v>57.69592780000001</v>
       </c>
       <c r="N80">
-        <v>147.5010670666667</v>
+        <v>146.7707388666667</v>
       </c>
       <c r="O80">
-        <v>44.25032012</v>
+        <v>44.03122166000001</v>
       </c>
       <c r="P80">
-        <v>103.2507469466667</v>
+        <v>102.7395172066667</v>
       </c>
       <c r="Q80">
-        <v>187.4507469466667</v>
+        <v>186.9395172066667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2438776610905091</v>
+        <v>0.2524972285879203</v>
       </c>
       <c r="T80">
-        <v>2.882271319156509</v>
+        <v>3.00769652886741</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.589300702571147</v>
+        <v>3.543866516462652</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08692331800346326</v>
+        <v>0.08829175056701452</v>
       </c>
       <c r="C81">
-        <v>508.6494581349507</v>
+        <v>452.2815739578671</v>
       </c>
       <c r="D81">
-        <v>1380.355458134951</v>
+        <v>1335.901573957867</v>
       </c>
       <c r="E81">
-        <v>257.0060000000001</v>
+        <v>268.9200000000001</v>
       </c>
       <c r="F81">
-        <v>941.2060000000001</v>
+        <v>953.1200000000001</v>
       </c>
       <c r="G81">
         <v>69.5</v>
@@ -7935,45 +7935,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M81">
-        <v>57.69592780000001</v>
+        <v>61.09499200000001</v>
       </c>
       <c r="N81">
-        <v>146.7707388666667</v>
+        <v>143.3716746666667</v>
       </c>
       <c r="O81">
-        <v>44.03122166000001</v>
+        <v>43.0115024</v>
       </c>
       <c r="P81">
-        <v>102.7395172066667</v>
+        <v>100.3601722666667</v>
       </c>
       <c r="Q81">
-        <v>186.9395172066667</v>
+        <v>184.5601722666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2524972285879203</v>
+        <v>0.2619787528350726</v>
       </c>
       <c r="T81">
-        <v>3.00769652886741</v>
+        <v>3.145664259549402</v>
       </c>
       <c r="U81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V81">
         <v>0.3</v>
       </c>
       <c r="W81">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.543866516462652</v>
+        <v>3.346700931995648</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08829175056701452</v>
+        <v>0.08811178313056577</v>
       </c>
       <c r="C82">
-        <v>452.2815739578671</v>
+        <v>446.049650292754</v>
       </c>
       <c r="D82">
-        <v>1335.901573957867</v>
+        <v>1341.583650292754</v>
       </c>
       <c r="E82">
-        <v>268.9200000000001</v>
+        <v>280.8340000000001</v>
       </c>
       <c r="F82">
-        <v>953.1200000000001</v>
+        <v>965.0340000000001</v>
       </c>
       <c r="G82">
         <v>69.5</v>
@@ -8017,28 +8017,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M82">
-        <v>61.09499200000001</v>
+        <v>61.85867940000001</v>
       </c>
       <c r="N82">
-        <v>143.3716746666667</v>
+        <v>142.6079872666667</v>
       </c>
       <c r="O82">
-        <v>43.0115024</v>
+        <v>42.78239618</v>
       </c>
       <c r="P82">
-        <v>100.3601722666667</v>
+        <v>99.82559108666666</v>
       </c>
       <c r="Q82">
-        <v>184.5601722666667</v>
+        <v>184.0255910866667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2619787528350726</v>
+        <v>0.2724583322661357</v>
       </c>
       <c r="T82">
-        <v>3.145664259549402</v>
+        <v>3.29815490925055</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.346700931995648</v>
+        <v>3.305383636538911</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08811178313056577</v>
+        <v>0.08793181569411704</v>
       </c>
       <c r="C83">
-        <v>446.049650292754</v>
+        <v>439.8662689795351</v>
       </c>
       <c r="D83">
-        <v>1341.583650292754</v>
+        <v>1347.314268979535</v>
       </c>
       <c r="E83">
-        <v>280.8340000000001</v>
+        <v>292.748</v>
       </c>
       <c r="F83">
-        <v>965.0340000000001</v>
+        <v>976.9480000000001</v>
       </c>
       <c r="G83">
         <v>69.5</v>
@@ -8099,28 +8099,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M83">
-        <v>61.85867940000001</v>
+        <v>62.62236680000001</v>
       </c>
       <c r="N83">
-        <v>142.6079872666667</v>
+        <v>141.8442998666667</v>
       </c>
       <c r="O83">
-        <v>42.78239618</v>
+        <v>42.55328996000001</v>
       </c>
       <c r="P83">
-        <v>99.82559108666666</v>
+        <v>99.29100990666669</v>
       </c>
       <c r="Q83">
-        <v>184.0255910866667</v>
+        <v>183.4910099066667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2724583322661357</v>
+        <v>0.2841023094117613</v>
       </c>
       <c r="T83">
-        <v>3.29815490925055</v>
+        <v>3.467588964474049</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.305383636538911</v>
+        <v>3.265074079995754</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08793181569411704</v>
+        <v>0.08775184825766828</v>
       </c>
       <c r="C84">
-        <v>439.8662689795351</v>
+        <v>433.7320547374781</v>
       </c>
       <c r="D84">
-        <v>1347.314268979535</v>
+        <v>1353.094054737478</v>
       </c>
       <c r="E84">
-        <v>292.748</v>
+        <v>304.6620000000001</v>
       </c>
       <c r="F84">
-        <v>976.9480000000001</v>
+        <v>988.8620000000002</v>
       </c>
       <c r="G84">
         <v>69.5</v>
@@ -8181,28 +8181,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M84">
-        <v>62.62236680000001</v>
+        <v>63.38605420000002</v>
       </c>
       <c r="N84">
-        <v>141.8442998666667</v>
+        <v>141.0806124666667</v>
       </c>
       <c r="O84">
-        <v>42.55328996000001</v>
+        <v>42.32418374</v>
       </c>
       <c r="P84">
-        <v>99.29100990666669</v>
+        <v>98.75642872666668</v>
       </c>
       <c r="Q84">
-        <v>183.4910099066667</v>
+        <v>182.9564287266667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2841023094117613</v>
+        <v>0.2971161662215783</v>
       </c>
       <c r="T84">
-        <v>3.467588964474049</v>
+        <v>3.656956437959135</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.265074079995754</v>
+        <v>3.225735838068094</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08775184825766828</v>
+        <v>0.08757188082121956</v>
       </c>
       <c r="C85">
-        <v>433.7320547374781</v>
+        <v>427.64764305186</v>
       </c>
       <c r="D85">
-        <v>1353.094054737478</v>
+        <v>1358.92364305186</v>
       </c>
       <c r="E85">
-        <v>304.6620000000001</v>
+        <v>316.5760000000001</v>
       </c>
       <c r="F85">
-        <v>988.8620000000002</v>
+        <v>1000.776</v>
       </c>
       <c r="G85">
         <v>69.5</v>
@@ -8263,28 +8263,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M85">
-        <v>63.38605420000002</v>
+        <v>64.14974160000001</v>
       </c>
       <c r="N85">
-        <v>141.0806124666667</v>
+        <v>140.3169250666667</v>
       </c>
       <c r="O85">
-        <v>42.32418374</v>
+        <v>42.09507752</v>
       </c>
       <c r="P85">
-        <v>98.75642872666668</v>
+        <v>98.22184754666668</v>
       </c>
       <c r="Q85">
-        <v>182.9564287266667</v>
+        <v>182.4218475466667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2971161662215783</v>
+        <v>0.3117567551326224</v>
       </c>
       <c r="T85">
-        <v>3.656956437959135</v>
+        <v>3.869994845629858</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.225735838068094</v>
+        <v>3.187334220948236</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08757188082121956</v>
+        <v>0.08739191338477081</v>
       </c>
       <c r="C86">
-        <v>427.6476430518601</v>
+        <v>421.6136804068899</v>
       </c>
       <c r="D86">
-        <v>1358.92364305186</v>
+        <v>1364.80368040689</v>
       </c>
       <c r="E86">
-        <v>316.576</v>
+        <v>328.49</v>
       </c>
       <c r="F86">
-        <v>1000.776</v>
+        <v>1012.69</v>
       </c>
       <c r="G86">
         <v>69.5</v>
@@ -8345,28 +8345,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M86">
-        <v>64.14974160000001</v>
+        <v>64.91342900000001</v>
       </c>
       <c r="N86">
-        <v>140.3169250666667</v>
+        <v>139.5532376666667</v>
       </c>
       <c r="O86">
-        <v>42.09507752</v>
+        <v>41.86597130000001</v>
       </c>
       <c r="P86">
-        <v>98.22184754666668</v>
+        <v>97.68726636666668</v>
       </c>
       <c r="Q86">
-        <v>182.4218475466667</v>
+        <v>181.8872663666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3117567551326221</v>
+        <v>0.3283494225651387</v>
       </c>
       <c r="T86">
-        <v>3.869994845629855</v>
+        <v>4.11143837432334</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.187334220948236</v>
+        <v>3.149836171290022</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08739191338477081</v>
+        <v>0.08721194594832206</v>
       </c>
       <c r="C87">
-        <v>421.6136804068899</v>
+        <v>415.6308245247046</v>
       </c>
       <c r="D87">
-        <v>1364.80368040689</v>
+        <v>1370.734824524705</v>
       </c>
       <c r="E87">
-        <v>328.49</v>
+        <v>340.404</v>
       </c>
       <c r="F87">
-        <v>1012.69</v>
+        <v>1024.604</v>
       </c>
       <c r="G87">
         <v>69.5</v>
@@ -8427,28 +8427,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M87">
-        <v>64.91342900000001</v>
+        <v>65.6771164</v>
       </c>
       <c r="N87">
-        <v>139.5532376666667</v>
+        <v>138.7895502666667</v>
       </c>
       <c r="O87">
-        <v>41.86597130000001</v>
+        <v>41.63686508000001</v>
       </c>
       <c r="P87">
-        <v>97.68726636666668</v>
+        <v>97.1526851866667</v>
       </c>
       <c r="Q87">
-        <v>181.8872663666667</v>
+        <v>181.3526851866667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3283494225651387</v>
+        <v>0.3473124710594433</v>
       </c>
       <c r="T87">
-        <v>4.11143837432334</v>
+        <v>4.387373835687322</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.149836171290022</v>
+        <v>3.113210169298278</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08721194594832206</v>
+        <v>0.08703197851187333</v>
       </c>
       <c r="C88">
-        <v>415.6308245247046</v>
+        <v>409.69974461062</v>
       </c>
       <c r="D88">
-        <v>1370.734824524705</v>
+        <v>1376.71774461062</v>
       </c>
       <c r="E88">
-        <v>340.404</v>
+        <v>352.318</v>
       </c>
       <c r="F88">
-        <v>1024.604</v>
+        <v>1036.518</v>
       </c>
       <c r="G88">
         <v>69.5</v>
@@ -8509,28 +8509,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M88">
-        <v>65.6771164</v>
+        <v>66.44080380000001</v>
       </c>
       <c r="N88">
-        <v>138.7895502666667</v>
+        <v>138.0258628666667</v>
       </c>
       <c r="O88">
-        <v>41.63686508000001</v>
+        <v>41.40775886</v>
       </c>
       <c r="P88">
-        <v>97.1526851866667</v>
+        <v>96.61810400666667</v>
       </c>
       <c r="Q88">
-        <v>181.3526851866667</v>
+        <v>180.8181040066667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3473124710594433</v>
+        <v>0.3691929116297948</v>
       </c>
       <c r="T88">
-        <v>4.387373835687322</v>
+        <v>4.705760906491918</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.113210169298278</v>
+        <v>3.077426144363814</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08703197851187333</v>
+        <v>0.08685201107542459</v>
       </c>
       <c r="C89">
-        <v>409.69974461062</v>
+        <v>403.8211216048394</v>
       </c>
       <c r="D89">
-        <v>1376.71774461062</v>
+        <v>1382.753121604839</v>
       </c>
       <c r="E89">
-        <v>352.318</v>
+        <v>364.232</v>
       </c>
       <c r="F89">
-        <v>1036.518</v>
+        <v>1048.432</v>
       </c>
       <c r="G89">
         <v>69.5</v>
@@ -8591,28 +8591,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M89">
-        <v>66.44080380000001</v>
+        <v>67.20449120000001</v>
       </c>
       <c r="N89">
-        <v>138.0258628666667</v>
+        <v>137.2621754666667</v>
       </c>
       <c r="O89">
-        <v>41.40775886</v>
+        <v>41.17865264</v>
       </c>
       <c r="P89">
-        <v>96.61810400666667</v>
+        <v>96.08352282666669</v>
       </c>
       <c r="Q89">
-        <v>180.8181040066667</v>
+        <v>180.2835228266667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3691929116297948</v>
+        <v>0.3947200922952049</v>
       </c>
       <c r="T89">
-        <v>4.705760906491918</v>
+        <v>5.077212489097279</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.077426144363814</v>
+        <v>3.042455392723316</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08685201107542459</v>
+        <v>0.08667204363897583</v>
       </c>
       <c r="C90">
-        <v>403.8211216048394</v>
+        <v>397.9956484408069</v>
       </c>
       <c r="D90">
-        <v>1382.753121604839</v>
+        <v>1388.841648440807</v>
       </c>
       <c r="E90">
-        <v>364.232</v>
+        <v>376.146</v>
       </c>
       <c r="F90">
-        <v>1048.432</v>
+        <v>1060.346</v>
       </c>
       <c r="G90">
         <v>69.5</v>
@@ -8673,28 +8673,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M90">
-        <v>67.20449120000001</v>
+        <v>67.9681786</v>
       </c>
       <c r="N90">
-        <v>137.2621754666667</v>
+        <v>136.4984880666667</v>
       </c>
       <c r="O90">
-        <v>41.17865264</v>
+        <v>40.94954642000001</v>
       </c>
       <c r="P90">
-        <v>96.08352282666669</v>
+        <v>95.54894164666669</v>
       </c>
       <c r="Q90">
-        <v>180.2835228266667</v>
+        <v>179.7489416466667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3947200922952049</v>
+        <v>0.424888578536144</v>
       </c>
       <c r="T90">
-        <v>5.077212489097279</v>
+        <v>5.516200723085434</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.042455392723316</v>
+        <v>3.008270500670246</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08667204363897583</v>
+        <v>0.09140607620252711</v>
       </c>
       <c r="C91">
-        <v>397.9956484408069</v>
+        <v>241.9161745215511</v>
       </c>
       <c r="D91">
-        <v>1388.841648440807</v>
+        <v>1244.676174521551</v>
       </c>
       <c r="E91">
-        <v>376.146</v>
+        <v>388.0600000000002</v>
       </c>
       <c r="F91">
-        <v>1060.346</v>
+        <v>1072.26</v>
       </c>
       <c r="G91">
         <v>69.5</v>
@@ -8755,45 +8755,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M91">
-        <v>67.9681786</v>
+        <v>77.09549400000002</v>
       </c>
       <c r="N91">
-        <v>136.4984880666667</v>
+        <v>127.3711726666667</v>
       </c>
       <c r="O91">
-        <v>40.94954642000001</v>
+        <v>38.2113518</v>
       </c>
       <c r="P91">
-        <v>95.54894164666669</v>
+        <v>89.15982086666668</v>
       </c>
       <c r="Q91">
-        <v>179.7489416466667</v>
+        <v>173.3598208666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.424888578536144</v>
+        <v>0.4610907620252711</v>
       </c>
       <c r="T91">
-        <v>5.516200723085434</v>
+        <v>6.042986603871219</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.3</v>
       </c>
       <c r="W91">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.008270500670246</v>
+        <v>2.652122141751458</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09140607620252711</v>
+        <v>0.09128070876607836</v>
       </c>
       <c r="C92">
-        <v>241.9161745215511</v>
+        <v>233.4331206400732</v>
       </c>
       <c r="D92">
-        <v>1244.676174521551</v>
+        <v>1248.107120640073</v>
       </c>
       <c r="E92">
-        <v>388.0600000000002</v>
+        <v>399.9740000000002</v>
       </c>
       <c r="F92">
-        <v>1072.26</v>
+        <v>1084.174</v>
       </c>
       <c r="G92">
         <v>69.5</v>
@@ -8837,28 +8837,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M92">
-        <v>77.09549400000002</v>
+        <v>77.95211060000003</v>
       </c>
       <c r="N92">
-        <v>127.3711726666667</v>
+        <v>126.5145560666667</v>
       </c>
       <c r="O92">
-        <v>38.2113518</v>
+        <v>37.95436682</v>
       </c>
       <c r="P92">
-        <v>89.15982086666668</v>
+        <v>88.56018924666668</v>
       </c>
       <c r="Q92">
-        <v>173.3598208666667</v>
+        <v>172.7601892466667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4610907620252711</v>
+        <v>0.5053378751786485</v>
       </c>
       <c r="T92">
-        <v>6.042986603871219</v>
+        <v>6.686836013720512</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.652122141751458</v>
+        <v>2.622977942391551</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09128070876607836</v>
+        <v>0.0911553413296296</v>
       </c>
       <c r="C93">
-        <v>233.4331206400732</v>
+        <v>224.9690338265023</v>
       </c>
       <c r="D93">
-        <v>1248.107120640073</v>
+        <v>1251.557033826502</v>
       </c>
       <c r="E93">
-        <v>399.9740000000002</v>
+        <v>411.8880000000001</v>
       </c>
       <c r="F93">
-        <v>1084.174</v>
+        <v>1096.088</v>
       </c>
       <c r="G93">
         <v>69.5</v>
@@ -8919,28 +8919,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M93">
-        <v>77.95211060000003</v>
+        <v>78.80872720000002</v>
       </c>
       <c r="N93">
-        <v>126.5145560666667</v>
+        <v>125.6579394666667</v>
       </c>
       <c r="O93">
-        <v>37.95436682</v>
+        <v>37.69738184</v>
       </c>
       <c r="P93">
-        <v>88.56018924666668</v>
+        <v>87.96055762666668</v>
       </c>
       <c r="Q93">
-        <v>172.7601892466667</v>
+        <v>172.1605576266667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5053378751786485</v>
+        <v>0.5606467666203704</v>
       </c>
       <c r="T93">
-        <v>6.686836013720512</v>
+        <v>7.491647776032131</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.622977942391551</v>
+        <v>2.594467312582948</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0911553413296296</v>
+        <v>0.09102997389318088</v>
       </c>
       <c r="C94">
-        <v>224.9690338265023</v>
+        <v>216.5240717983293</v>
       </c>
       <c r="D94">
-        <v>1251.557033826502</v>
+        <v>1255.026071798329</v>
       </c>
       <c r="E94">
-        <v>411.8880000000001</v>
+        <v>423.8020000000001</v>
       </c>
       <c r="F94">
-        <v>1096.088</v>
+        <v>1108.002</v>
       </c>
       <c r="G94">
         <v>69.5</v>
@@ -9001,28 +9001,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M94">
-        <v>78.80872720000002</v>
+        <v>79.66534380000002</v>
       </c>
       <c r="N94">
-        <v>125.6579394666667</v>
+        <v>124.8013228666667</v>
       </c>
       <c r="O94">
-        <v>37.69738184</v>
+        <v>37.44039686</v>
       </c>
       <c r="P94">
-        <v>87.96055762666668</v>
+        <v>87.36092600666669</v>
       </c>
       <c r="Q94">
-        <v>172.1605576266667</v>
+        <v>171.5609260066667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5606467666203704</v>
+        <v>0.6317581984740128</v>
       </c>
       <c r="T94">
-        <v>7.491647776032131</v>
+        <v>8.526405756147067</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.594467312582948</v>
+        <v>2.566569814598185</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09102997389318088</v>
+        <v>0.09090460645673212</v>
       </c>
       <c r="C95">
-        <v>216.5240717983293</v>
+        <v>208.0983940265401</v>
       </c>
       <c r="D95">
-        <v>1255.026071798329</v>
+        <v>1258.51439402654</v>
       </c>
       <c r="E95">
-        <v>423.8020000000001</v>
+        <v>435.7160000000001</v>
       </c>
       <c r="F95">
-        <v>1108.002</v>
+        <v>1119.916</v>
       </c>
       <c r="G95">
         <v>69.5</v>
@@ -9083,28 +9083,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M95">
-        <v>79.66534380000002</v>
+        <v>80.52196040000001</v>
       </c>
       <c r="N95">
-        <v>124.8013228666667</v>
+        <v>123.9447062666667</v>
       </c>
       <c r="O95">
-        <v>37.44039686</v>
+        <v>37.18341188</v>
       </c>
       <c r="P95">
-        <v>87.36092600666669</v>
+        <v>86.76129438666669</v>
       </c>
       <c r="Q95">
-        <v>171.5609260066667</v>
+        <v>170.9612943866667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6317581984740128</v>
+        <v>0.7265734409455361</v>
       </c>
       <c r="T95">
-        <v>8.526405756147067</v>
+        <v>9.906083062966983</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.566569814598185</v>
+        <v>2.539265880400332</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09090460645673212</v>
+        <v>0.09077923902028338</v>
       </c>
       <c r="C96">
-        <v>208.0983940265401</v>
+        <v>199.6921617600447</v>
       </c>
       <c r="D96">
-        <v>1258.51439402654</v>
+        <v>1262.022161760045</v>
       </c>
       <c r="E96">
-        <v>435.7160000000001</v>
+        <v>447.6300000000001</v>
       </c>
       <c r="F96">
-        <v>1119.916</v>
+        <v>1131.83</v>
       </c>
       <c r="G96">
         <v>69.5</v>
@@ -9165,28 +9165,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M96">
-        <v>80.52196040000001</v>
+        <v>81.37857700000002</v>
       </c>
       <c r="N96">
-        <v>123.9447062666667</v>
+        <v>123.0880896666667</v>
       </c>
       <c r="O96">
-        <v>37.18341188</v>
+        <v>36.9264269</v>
       </c>
       <c r="P96">
-        <v>86.76129438666669</v>
+        <v>86.16166276666667</v>
       </c>
       <c r="Q96">
-        <v>170.9612943866667</v>
+        <v>170.3616627666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7265734409455361</v>
+        <v>0.8593147804056688</v>
       </c>
       <c r="T96">
-        <v>9.906083062966983</v>
+        <v>11.83763129251487</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.539265880400332</v>
+        <v>2.512536765869802</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09077923902028338</v>
+        <v>0.09327467158383465</v>
       </c>
       <c r="C97">
-        <v>199.6921617600447</v>
+        <v>121.441921964934</v>
       </c>
       <c r="D97">
-        <v>1262.022161760045</v>
+        <v>1195.685921964934</v>
       </c>
       <c r="E97">
-        <v>447.6300000000001</v>
+        <v>459.5440000000001</v>
       </c>
       <c r="F97">
-        <v>1131.83</v>
+        <v>1143.744</v>
       </c>
       <c r="G97">
         <v>69.5</v>
@@ -9247,45 +9247,45 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M97">
-        <v>81.37857700000002</v>
+        <v>86.69579520000002</v>
       </c>
       <c r="N97">
-        <v>123.0880896666667</v>
+        <v>117.7708714666667</v>
       </c>
       <c r="O97">
-        <v>36.9264269</v>
+        <v>35.33126144</v>
       </c>
       <c r="P97">
-        <v>86.16166276666667</v>
+        <v>82.43961002666668</v>
       </c>
       <c r="Q97">
-        <v>170.3616627666667</v>
+        <v>166.6396100266667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8593147804056688</v>
+        <v>1.058426789595868</v>
       </c>
       <c r="T97">
-        <v>11.83763129251487</v>
+        <v>14.7349536368367</v>
       </c>
       <c r="U97">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V97">
         <v>0.3</v>
       </c>
       <c r="W97">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.512536765869802</v>
+        <v>2.358438101813116</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09327467158383465</v>
+        <v>0.09317660414738592</v>
       </c>
       <c r="C98">
-        <v>121.441921964934</v>
+        <v>112.0029379622847</v>
       </c>
       <c r="D98">
-        <v>1195.685921964934</v>
+        <v>1198.160937962285</v>
       </c>
       <c r="E98">
-        <v>459.5440000000001</v>
+        <v>471.4580000000001</v>
       </c>
       <c r="F98">
-        <v>1143.744</v>
+        <v>1155.658</v>
       </c>
       <c r="G98">
         <v>69.5</v>
@@ -9329,28 +9329,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M98">
-        <v>86.69579520000002</v>
+        <v>87.59887640000002</v>
       </c>
       <c r="N98">
-        <v>117.7708714666667</v>
+        <v>116.8677902666667</v>
       </c>
       <c r="O98">
-        <v>35.33126144</v>
+        <v>35.06033708</v>
       </c>
       <c r="P98">
-        <v>82.43961002666668</v>
+        <v>81.80745318666666</v>
       </c>
       <c r="Q98">
-        <v>166.6396100266667</v>
+        <v>166.0074531866667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.058426789595865</v>
+        <v>1.390280138246196</v>
       </c>
       <c r="T98">
-        <v>14.73495363683666</v>
+        <v>19.56382421070635</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.358438101813116</v>
+        <v>2.334124306949063</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09317660414738592</v>
+        <v>0.09307853671093717</v>
       </c>
       <c r="C99">
-        <v>112.0029379622847</v>
+        <v>102.5742215563475</v>
       </c>
       <c r="D99">
-        <v>1198.160937962285</v>
+        <v>1200.646221556348</v>
       </c>
       <c r="E99">
-        <v>471.4580000000001</v>
+        <v>483.3720000000001</v>
       </c>
       <c r="F99">
-        <v>1155.658</v>
+        <v>1167.572</v>
       </c>
       <c r="G99">
         <v>69.5</v>
@@ -9411,28 +9411,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M99">
-        <v>87.59887640000002</v>
+        <v>88.50195760000001</v>
       </c>
       <c r="N99">
-        <v>116.8677902666667</v>
+        <v>115.9647090666667</v>
       </c>
       <c r="O99">
-        <v>35.06033708</v>
+        <v>34.78941272</v>
       </c>
       <c r="P99">
-        <v>81.80745318666666</v>
+        <v>81.17529634666668</v>
       </c>
       <c r="Q99">
-        <v>166.0074531866667</v>
+        <v>165.3752963466667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.390280138246196</v>
+        <v>2.053986835546857</v>
       </c>
       <c r="T99">
-        <v>19.56382421070635</v>
+        <v>29.22156535844573</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.334124306949063</v>
+        <v>2.310306711980195</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09307853671093717</v>
+        <v>0.09298046927448843</v>
       </c>
       <c r="C100">
-        <v>102.5742215563475</v>
+        <v>93.1558367725695</v>
       </c>
       <c r="D100">
-        <v>1200.646221556348</v>
+        <v>1203.14183677257</v>
       </c>
       <c r="E100">
-        <v>483.3720000000001</v>
+        <v>495.2860000000001</v>
       </c>
       <c r="F100">
-        <v>1167.572</v>
+        <v>1179.486</v>
       </c>
       <c r="G100">
         <v>69.5</v>
@@ -9493,28 +9493,28 @@
         <v>204.4666666666667</v>
       </c>
       <c r="M100">
-        <v>88.50195760000001</v>
+        <v>89.40503880000001</v>
       </c>
       <c r="N100">
-        <v>115.9647090666667</v>
+        <v>115.0616278666667</v>
       </c>
       <c r="O100">
-        <v>34.78941272</v>
+        <v>34.51848836000001</v>
       </c>
       <c r="P100">
-        <v>81.17529634666668</v>
+        <v>80.54313950666668</v>
       </c>
       <c r="Q100">
-        <v>165.3752963466667</v>
+        <v>164.7431395066667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.053986835546857</v>
+        <v>4.045106927448839</v>
       </c>
       <c r="T100">
-        <v>29.22156535844573</v>
+        <v>58.19478880166388</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.310306711980195</v>
+        <v>2.286970280546052</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09298046927448843</v>
-      </c>
-      <c r="C101">
-        <v>93.1558367725695</v>
-      </c>
-      <c r="D101">
-        <v>1203.14183677257</v>
-      </c>
-      <c r="E101">
-        <v>495.2860000000001</v>
-      </c>
-      <c r="F101">
-        <v>1179.486</v>
-      </c>
-      <c r="G101">
-        <v>69.5</v>
-      </c>
-      <c r="H101">
-        <v>507.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>288.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>84.19999999999999</v>
-      </c>
-      <c r="L101">
-        <v>204.4666666666667</v>
-      </c>
-      <c r="M101">
-        <v>89.40503880000001</v>
-      </c>
-      <c r="N101">
-        <v>115.0616278666667</v>
-      </c>
-      <c r="O101">
-        <v>34.51848836000001</v>
-      </c>
-      <c r="P101">
-        <v>80.54313950666668</v>
-      </c>
-      <c r="Q101">
-        <v>164.7431395066667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.045106927448839</v>
-      </c>
-      <c r="T101">
-        <v>58.19478880166388</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.286970280546052</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
